--- a/results/block2_results/stenosis/Synthetic_1/branches/dataframes/dataset_Synthetic_0_Synthetic_1.xlsx
+++ b/results/block2_results/stenosis/Synthetic_1/branches/dataframes/dataset_Synthetic_0_Synthetic_1.xlsx
@@ -561,14 +561,14 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4956573926921</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949668794302</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="b">
@@ -617,14 +617,14 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>314.1592653589793</v>
+        <v>316.495663736169</v>
       </c>
       <c r="M3" t="n">
         <v>0.001928344560479429</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949668794302</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="b">
@@ -673,14 +673,14 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>314.1592653589793</v>
+        <v>316.497247714403</v>
       </c>
       <c r="M4" t="n">
         <v>0.004646351162764988</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949668794302</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="b">
@@ -729,14 +729,14 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6184335045709</v>
       </c>
       <c r="M5" t="n">
         <v>0.4872934011940112</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493042216251</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="b">
@@ -785,14 +785,14 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6184254719337</v>
       </c>
       <c r="M6" t="n">
         <v>0.4873054643259579</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493042216251</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="b">
@@ -841,14 +841,14 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5201153989869</v>
       </c>
       <c r="M7" t="n">
         <v>0.5074220832735221</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493042216251</v>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="b">
@@ -897,14 +897,14 @@
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930957021824</v>
       </c>
       <c r="M8" t="n">
         <v>0.9984023884506892</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949752365325</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="b">
@@ -953,14 +953,14 @@
         <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4969575256447</v>
       </c>
       <c r="M9" t="n">
         <v>1.000330733011169</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949752365325</v>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="b">
@@ -1009,14 +1009,14 @@
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4969704139756</v>
       </c>
       <c r="M10" t="n">
         <v>1.003077349480442</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949752365325</v>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="b">
@@ -1065,14 +1065,14 @@
         <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6141132411262</v>
       </c>
       <c r="M11" t="n">
         <v>1.485732028904525</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199964961624</v>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="b">
@@ -1121,14 +1121,14 @@
         <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6141106837076</v>
       </c>
       <c r="M12" t="n">
         <v>1.485744092036461</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199964961624</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="b">
@@ -1177,14 +1177,14 @@
         <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200386636117</v>
       </c>
       <c r="M13" t="n">
         <v>1.505858803798518</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199964961624</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="b">
@@ -1233,14 +1233,14 @@
         <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930385944998</v>
       </c>
       <c r="M14" t="n">
         <v>1.99482113476955</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930118995226</v>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="b">
@@ -1289,14 +1289,14 @@
         <v>13</v>
       </c>
       <c r="L15" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949762732821</v>
       </c>
       <c r="M15" t="n">
         <v>1.996747560665615</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930118995226</v>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="b">
@@ -1345,14 +1345,14 @@
         <v>14</v>
       </c>
       <c r="L16" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494978843572</v>
       </c>
       <c r="M16" t="n">
         <v>2.001504518746744</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930118995226</v>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="b">
@@ -1401,14 +1401,14 @@
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930075848398</v>
       </c>
       <c r="M17" t="n">
         <v>2.484122958554898</v>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203930397376</v>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="b">
@@ -1457,14 +1457,14 @@
         <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6130640517828</v>
       </c>
       <c r="M18" t="n">
         <v>2.484135021686845</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203930397376</v>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="b">
@@ -1513,14 +1513,14 @@
         <v>17</v>
       </c>
       <c r="L19" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203838027119</v>
       </c>
       <c r="M19" t="n">
         <v>2.504259294323816</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203930397376</v>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="b">
@@ -1569,14 +1569,14 @@
         <v>18</v>
       </c>
       <c r="L20" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930343464838</v>
       </c>
       <c r="M20" t="n">
         <v>2.993212087468462</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949669798136</v>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="b">
@@ -1625,14 +1625,14 @@
         <v>19</v>
       </c>
       <c r="L21" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935520373542</v>
       </c>
       <c r="M21" t="n">
         <v>2.99514042070942</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949669798136</v>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="b">
@@ -1681,14 +1681,14 @@
         <v>20</v>
       </c>
       <c r="L22" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949725584177</v>
       </c>
       <c r="M22" t="n">
         <v>2.999895471454191</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949669798136</v>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="b">
@@ -1737,14 +1737,14 @@
         <v>21</v>
       </c>
       <c r="L23" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128876776233</v>
       </c>
       <c r="M23" t="n">
         <v>3.482519633306967</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199900746123</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="b">
@@ -1793,14 +1793,14 @@
         <v>22</v>
       </c>
       <c r="L24" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128795357786</v>
       </c>
       <c r="M24" t="n">
         <v>3.482531696438911</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199900746123</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="b">
@@ -1849,14 +1849,14 @@
         <v>23</v>
       </c>
       <c r="L25" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5204015809694</v>
       </c>
       <c r="M25" t="n">
         <v>3.502648340342993</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199900746123</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="b">
@@ -1905,14 +1905,14 @@
         <v>24</v>
       </c>
       <c r="L26" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930365246085</v>
       </c>
       <c r="M26" t="n">
         <v>3.991603040835658</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949672377866</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="b">
@@ -1961,14 +1961,14 @@
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935514579993</v>
       </c>
       <c r="M27" t="n">
         <v>3.993531374076627</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949672377866</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="b">
@@ -2017,14 +2017,14 @@
         <v>26</v>
       </c>
       <c r="L28" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949767855666</v>
       </c>
       <c r="M28" t="n">
         <v>3.998292146830513</v>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949672377866</v>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="b">
@@ -2073,14 +2073,14 @@
         <v>27</v>
       </c>
       <c r="L29" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493007424782</v>
       </c>
       <c r="M29" t="n">
         <v>4.480914401335076</v>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203902427795</v>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="b">
@@ -2129,14 +2129,14 @@
         <v>28</v>
       </c>
       <c r="L30" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200099873713</v>
       </c>
       <c r="M30" t="n">
         <v>4.480926464467022</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203902427795</v>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="b">
@@ -2185,14 +2185,14 @@
         <v>29</v>
       </c>
       <c r="L31" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200129880708</v>
       </c>
       <c r="M31" t="n">
         <v>4.501041176229076</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203902427795</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="b">
@@ -2241,14 +2241,14 @@
         <v>30</v>
       </c>
       <c r="L32" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930382973014</v>
       </c>
       <c r="M32" t="n">
         <v>4.989999692504057</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949672078131</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="b">
@@ -2297,14 +2297,14 @@
         <v>31</v>
       </c>
       <c r="L33" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935585418855</v>
       </c>
       <c r="M33" t="n">
         <v>4.991926118400122</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949672078131</v>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="b">
@@ -2353,14 +2353,14 @@
         <v>32</v>
       </c>
       <c r="L34" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949722830236</v>
       </c>
       <c r="M34" t="n">
         <v>4.996683076481261</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949672078131</v>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="b">
@@ -2409,26 +2409,20 @@
         <v>33</v>
       </c>
       <c r="L35" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930021386068</v>
       </c>
       <c r="M35" t="n">
         <v>5.479307238334034</v>
       </c>
-      <c r="N35" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P35" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5200024306247</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="b">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2471,26 +2465,20 @@
         <v>34</v>
       </c>
       <c r="L36" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612849690406</v>
       </c>
       <c r="M36" t="n">
         <v>5.479319301465971</v>
       </c>
-      <c r="N36" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P36" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5200024306247</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="b">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2533,26 +2521,20 @@
         <v>35</v>
       </c>
       <c r="L37" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930389602211</v>
       </c>
       <c r="M37" t="n">
         <v>5.499435945370053</v>
       </c>
-      <c r="N37" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P37" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5200024306247</v>
+      </c>
+      <c r="P37" t="inlineStr"/>
       <c r="Q37" t="b">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2595,26 +2577,20 @@
         <v>36</v>
       </c>
       <c r="L38" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930383625305</v>
       </c>
       <c r="M38" t="n">
         <v>5.988388738514699</v>
       </c>
-      <c r="N38" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P38" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4949730977892</v>
+      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="b">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2657,26 +2633,20 @@
         <v>37</v>
       </c>
       <c r="L39" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935586468697</v>
       </c>
       <c r="M39" t="n">
         <v>5.990315164410778</v>
       </c>
-      <c r="N39" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P39" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4949730977892</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="b">
-        <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2719,26 +2689,20 @@
         <v>38</v>
       </c>
       <c r="L40" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949697132778</v>
       </c>
       <c r="M40" t="n">
         <v>5.995075937164665</v>
       </c>
-      <c r="N40" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P40" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4949730977892</v>
+      </c>
+      <c r="P40" t="inlineStr"/>
       <c r="Q40" t="b">
-        <v>1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2781,26 +2745,20 @@
         <v>39</v>
       </c>
       <c r="L41" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930027321008</v>
       </c>
       <c r="M41" t="n">
         <v>6.477696284321018</v>
       </c>
-      <c r="N41" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P41" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5199976203734</v>
+      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="b">
-        <v>1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2843,26 +2801,20 @@
         <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128425862997</v>
       </c>
       <c r="M42" t="n">
         <v>6.477708347452955</v>
       </c>
-      <c r="N42" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P42" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5199976203734</v>
+      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="b">
-        <v>1</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2905,26 +2857,20 @@
         <v>41</v>
       </c>
       <c r="L43" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203881166635</v>
       </c>
       <c r="M43" t="n">
         <v>6.497828805723429</v>
       </c>
-      <c r="N43" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P43" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5199976203734</v>
+      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="b">
-        <v>1</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2967,26 +2913,20 @@
         <v>42</v>
       </c>
       <c r="L44" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930372860184</v>
       </c>
       <c r="M44" t="n">
         <v>6.986781598868074</v>
       </c>
-      <c r="N44" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P44" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4949723935873</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="b">
-        <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3029,26 +2969,20 @@
         <v>43</v>
       </c>
       <c r="L45" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935613312356</v>
       </c>
       <c r="M45" t="n">
         <v>6.988708024764139</v>
       </c>
-      <c r="N45" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P45" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4949723935873</v>
+      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="b">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3091,26 +3025,20 @@
         <v>44</v>
       </c>
       <c r="L46" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930126274455</v>
       </c>
       <c r="M46" t="n">
         <v>6.993464982845278</v>
       </c>
-      <c r="N46" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P46" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4949723935873</v>
+      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="b">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3153,26 +3081,20 @@
         <v>45</v>
       </c>
       <c r="L47" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128491637729</v>
       </c>
       <c r="M47" t="n">
         <v>7.476085330001632</v>
       </c>
-      <c r="N47" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P47" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5199980062439</v>
+      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="b">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3215,26 +3137,20 @@
         <v>46</v>
       </c>
       <c r="L48" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128480980692</v>
       </c>
       <c r="M48" t="n">
         <v>7.476097393133569</v>
       </c>
-      <c r="N48" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P48" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5199980062439</v>
+      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="b">
-        <v>1</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3277,26 +3193,20 @@
         <v>47</v>
       </c>
       <c r="L49" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203733450849</v>
       </c>
       <c r="M49" t="n">
         <v>7.496221665770551</v>
       </c>
-      <c r="N49" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P49" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5199980062439</v>
+      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="b">
-        <v>1</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3339,26 +3249,20 @@
         <v>48</v>
       </c>
       <c r="L50" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935564731936</v>
       </c>
       <c r="M50" t="n">
         <v>7.985174458915196</v>
       </c>
-      <c r="N50" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P50" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.494972739798</v>
+      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="b">
-        <v>1</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3401,26 +3305,20 @@
         <v>49</v>
       </c>
       <c r="L51" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935611051667</v>
       </c>
       <c r="M51" t="n">
         <v>7.987100884811261</v>
       </c>
-      <c r="N51" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P51" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.494972739798</v>
+      </c>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="b">
-        <v>1</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3463,26 +3361,20 @@
         <v>50</v>
       </c>
       <c r="L52" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949722373054</v>
       </c>
       <c r="M52" t="n">
         <v>7.991857842892394</v>
       </c>
-      <c r="N52" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P52" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.494972739798</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
       <c r="Q52" t="b">
-        <v>1</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3525,26 +3417,20 @@
         <v>51</v>
       </c>
       <c r="L53" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930090131705</v>
       </c>
       <c r="M53" t="n">
         <v>8.474482004745166</v>
       </c>
-      <c r="N53" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P53" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930379955985</v>
+      </c>
+      <c r="P53" t="inlineStr"/>
       <c r="Q53" t="b">
-        <v>1</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3587,26 +3473,20 @@
         <v>52</v>
       </c>
       <c r="L54" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128435143209</v>
       </c>
       <c r="M54" t="n">
         <v>8.47449406787711</v>
       </c>
-      <c r="N54" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P54" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930379955985</v>
+      </c>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="b">
-        <v>1</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3649,26 +3529,20 @@
         <v>53</v>
       </c>
       <c r="L55" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199981412842</v>
       </c>
       <c r="M55" t="n">
         <v>8.494614501195789</v>
       </c>
-      <c r="N55" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P55" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930379955985</v>
+      </c>
+      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="b">
-        <v>1</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3711,26 +3585,20 @@
         <v>54</v>
       </c>
       <c r="L56" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493041840334</v>
       </c>
       <c r="M56" t="n">
         <v>8.983571110122762</v>
       </c>
-      <c r="N56" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P56" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4949715211828</v>
+      </c>
+      <c r="P56" t="inlineStr"/>
       <c r="Q56" t="b">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3773,26 +3641,20 @@
         <v>55</v>
       </c>
       <c r="L57" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935596884258</v>
       </c>
       <c r="M57" t="n">
         <v>8.985493721329048</v>
       </c>
-      <c r="N57" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P57" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4949715211828</v>
+      </c>
+      <c r="P57" t="inlineStr"/>
       <c r="Q57" t="b">
-        <v>1</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3835,26 +3697,20 @@
         <v>56</v>
       </c>
       <c r="L58" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930115302025</v>
       </c>
       <c r="M58" t="n">
         <v>8.990254494082935</v>
       </c>
-      <c r="N58" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P58" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4949715211828</v>
+      </c>
+      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="b">
-        <v>1</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3897,26 +3753,20 @@
         <v>57</v>
       </c>
       <c r="L59" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930056257696</v>
       </c>
       <c r="M59" t="n">
         <v>9.472874841239308</v>
       </c>
-      <c r="N59" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P59" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5203741138454</v>
+      </c>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="b">
-        <v>1</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3959,26 +3809,20 @@
         <v>58</v>
       </c>
       <c r="L60" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128418010185</v>
       </c>
       <c r="M60" t="n">
         <v>9.472886904371245</v>
       </c>
-      <c r="N60" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P60" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5203741138454</v>
+      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="b">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4021,26 +3865,20 @@
         <v>59</v>
       </c>
       <c r="L61" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203859866261</v>
       </c>
       <c r="M61" t="n">
         <v>9.493007362641711</v>
       </c>
-      <c r="N61" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P61" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5203741138454</v>
+      </c>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="b">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4083,26 +3921,20 @@
         <v>60</v>
       </c>
       <c r="L62" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930439535654</v>
       </c>
       <c r="M62" t="n">
         <v>9.981960155786357</v>
       </c>
-      <c r="N62" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P62" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930107030344</v>
+      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="b">
-        <v>1</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4145,26 +3977,20 @@
         <v>61</v>
       </c>
       <c r="L63" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949751289681</v>
       </c>
       <c r="M63" t="n">
         <v>9.983886581682421</v>
       </c>
-      <c r="N63" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P63" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930107030344</v>
+      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="b">
-        <v>1</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4207,26 +4033,20 @@
         <v>62</v>
       </c>
       <c r="L64" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949668794302</v>
       </c>
       <c r="M64" t="n">
         <v>9.988643539763547</v>
       </c>
-      <c r="N64" t="n">
-        <v>314.1592653589793</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P64" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930107030344</v>
+      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="b">
-        <v>1</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4269,25 +4089,25 @@
         <v>63</v>
       </c>
       <c r="L65" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128459868684</v>
       </c>
       <c r="M65" t="n">
         <v>10.47126770161633</v>
       </c>
       <c r="N65" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6184335045709</v>
       </c>
       <c r="O65" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203775551237</v>
       </c>
       <c r="P65" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0694055298472</v>
       </c>
       <c r="Q65" t="b">
         <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>-2.628189645560708</v>
       </c>
     </row>
     <row r="66">
@@ -4331,25 +4151,25 @@
         <v>64</v>
       </c>
       <c r="L66" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128506817055</v>
       </c>
       <c r="M66" t="n">
         <v>10.47127976474827</v>
       </c>
       <c r="N66" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6184335045709</v>
       </c>
       <c r="O66" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203775551237</v>
       </c>
       <c r="P66" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0694055298472</v>
       </c>
       <c r="Q66" t="b">
         <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>-2.628191089817533</v>
       </c>
     </row>
     <row r="67">
@@ -4393,25 +4213,25 @@
         <v>65</v>
       </c>
       <c r="L67" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493042216251</v>
       </c>
       <c r="M67" t="n">
         <v>10.49140019806696</v>
       </c>
       <c r="N67" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6184254719337</v>
       </c>
       <c r="O67" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203775551237</v>
       </c>
       <c r="P67" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0694015135287</v>
       </c>
       <c r="Q67" t="b">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.638316389468243</v>
       </c>
     </row>
     <row r="68">
@@ -4455,25 +4275,25 @@
         <v>66</v>
       </c>
       <c r="L68" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930423463633</v>
       </c>
       <c r="M68" t="n">
         <v>10.98035680699392</v>
       </c>
       <c r="N68" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930957021824</v>
       </c>
       <c r="O68" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494972694702</v>
       </c>
       <c r="P68" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940341984422</v>
       </c>
       <c r="Q68" t="b">
         <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>0.0003133872906624369</v>
       </c>
     </row>
     <row r="69">
@@ -4517,25 +4337,25 @@
         <v>67</v>
       </c>
       <c r="L69" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935605827587</v>
       </c>
       <c r="M69" t="n">
         <v>10.98228323288999</v>
       </c>
       <c r="N69" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930957021824</v>
       </c>
       <c r="O69" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494972694702</v>
       </c>
       <c r="P69" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940341984422</v>
       </c>
       <c r="Q69" t="b">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>0.0001496444268611619</v>
       </c>
     </row>
     <row r="70">
@@ -4579,25 +4399,25 @@
         <v>68</v>
       </c>
       <c r="L70" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949752365325</v>
       </c>
       <c r="M70" t="n">
         <v>10.98704019097113</v>
       </c>
       <c r="N70" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930957021824</v>
       </c>
       <c r="O70" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494972694702</v>
       </c>
       <c r="P70" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940341984422</v>
       </c>
       <c r="Q70" t="b">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>-0.0002973320153198955</v>
       </c>
     </row>
     <row r="71">
@@ -4641,25 +4461,25 @@
         <v>69</v>
       </c>
       <c r="L71" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128470552172</v>
       </c>
       <c r="M71" t="n">
         <v>11.46966053812748</v>
       </c>
       <c r="N71" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6141132411262</v>
       </c>
       <c r="O71" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930394303518</v>
       </c>
       <c r="P71" t="n">
-        <v>314.1592653589793</v>
+        <v>325.053576335739</v>
       </c>
       <c r="Q71" t="b">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>-2.633187678156035</v>
       </c>
     </row>
     <row r="72">
@@ -4703,25 +4523,25 @@
         <v>70</v>
       </c>
       <c r="L72" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128427491318</v>
       </c>
       <c r="M72" t="n">
         <v>11.46967260125943</v>
       </c>
       <c r="N72" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6141132411262</v>
       </c>
       <c r="O72" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930394303518</v>
       </c>
       <c r="P72" t="n">
-        <v>314.1592653589793</v>
+        <v>325.053576335739</v>
       </c>
       <c r="Q72" t="b">
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>-2.633186353425065</v>
       </c>
     </row>
     <row r="73">
@@ -4765,25 +4585,25 @@
         <v>71</v>
       </c>
       <c r="L73" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199964961624</v>
       </c>
       <c r="M73" t="n">
         <v>11.4897930345781</v>
       </c>
       <c r="N73" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6141106837076</v>
       </c>
       <c r="O73" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930394303518</v>
       </c>
       <c r="P73" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0535750570297</v>
       </c>
       <c r="Q73" t="b">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.625283711883508</v>
       </c>
     </row>
     <row r="74">
@@ -4827,25 +4647,25 @@
         <v>72</v>
       </c>
       <c r="L74" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930414946184</v>
       </c>
       <c r="M74" t="n">
         <v>11.97874582880904</v>
       </c>
       <c r="N74" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930385944998</v>
       </c>
       <c r="O74" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949723969125</v>
       </c>
       <c r="P74" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940054957061</v>
       </c>
       <c r="Q74" t="b">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>0.0003045874711782304</v>
       </c>
     </row>
     <row r="75">
@@ -4889,25 +4709,25 @@
         <v>73</v>
       </c>
       <c r="L75" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949749845024</v>
       </c>
       <c r="M75" t="n">
         <v>11.9806722547051</v>
       </c>
       <c r="N75" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930385944998</v>
       </c>
       <c r="O75" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949723969125</v>
       </c>
       <c r="P75" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940054957061</v>
       </c>
       <c r="Q75" t="b">
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>-0.0003063213771747897</v>
       </c>
     </row>
     <row r="76">
@@ -4951,25 +4771,25 @@
         <v>74</v>
       </c>
       <c r="L76" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930118995226</v>
       </c>
       <c r="M76" t="n">
         <v>11.98542921278623</v>
       </c>
       <c r="N76" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930385944998</v>
       </c>
       <c r="O76" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949723969125</v>
       </c>
       <c r="P76" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940054957061</v>
       </c>
       <c r="Q76" t="b">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>0.0003139383894512626</v>
       </c>
     </row>
     <row r="77">
@@ -5013,25 +4833,25 @@
         <v>75</v>
       </c>
       <c r="L77" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930069900548</v>
       </c>
       <c r="M77" t="n">
         <v>12.468053374639</v>
       </c>
       <c r="N77" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930075848398</v>
       </c>
       <c r="O77" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203929243579</v>
       </c>
       <c r="P77" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5067002545989</v>
       </c>
       <c r="Q77" t="b">
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>0.004326374302032754</v>
       </c>
     </row>
     <row r="78">
@@ -5075,25 +4895,25 @@
         <v>76</v>
       </c>
       <c r="L78" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128424507029</v>
       </c>
       <c r="M78" t="n">
         <v>12.46806543777095</v>
       </c>
       <c r="N78" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930075848398</v>
       </c>
       <c r="O78" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203929243579</v>
       </c>
       <c r="P78" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5067002545989</v>
       </c>
       <c r="Q78" t="b">
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>-5.404669848171872</v>
       </c>
     </row>
     <row r="79">
@@ -5137,25 +4957,25 @@
         <v>77</v>
       </c>
       <c r="L79" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203930397376</v>
       </c>
       <c r="M79" t="n">
         <v>12.48818589604141</v>
       </c>
       <c r="N79" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6130640517828</v>
       </c>
       <c r="O79" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203929243579</v>
       </c>
       <c r="P79" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0667284880703</v>
       </c>
       <c r="Q79" t="b">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.629101873354711</v>
       </c>
     </row>
     <row r="80">
@@ -5199,25 +5019,25 @@
         <v>78</v>
       </c>
       <c r="L80" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935545092449</v>
       </c>
       <c r="M80" t="n">
         <v>12.97713868918606</v>
       </c>
       <c r="N80" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930343464838</v>
       </c>
       <c r="O80" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949720419701</v>
       </c>
       <c r="P80" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940031942269</v>
       </c>
       <c r="Q80" t="b">
         <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>0.0001417672933712311</v>
       </c>
     </row>
     <row r="81">
@@ -5261,25 +5081,25 @@
         <v>79</v>
       </c>
       <c r="L81" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935641991925</v>
       </c>
       <c r="M81" t="n">
         <v>12.97906511508213</v>
       </c>
       <c r="N81" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930343464838</v>
       </c>
       <c r="O81" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949720419701</v>
       </c>
       <c r="P81" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940031942269</v>
       </c>
       <c r="Q81" t="b">
         <v>1</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>0.0001387056405399711</v>
       </c>
     </row>
     <row r="82">
@@ -5323,25 +5143,25 @@
         <v>80</v>
       </c>
       <c r="L82" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949669798136</v>
       </c>
       <c r="M82" t="n">
         <v>12.98382207316326</v>
       </c>
       <c r="N82" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930343464838</v>
       </c>
       <c r="O82" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949720419701</v>
       </c>
       <c r="P82" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940031942269</v>
       </c>
       <c r="Q82" t="b">
         <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>-0.0003045193832873494</v>
       </c>
     </row>
     <row r="83">
@@ -5385,25 +5205,25 @@
         <v>81</v>
       </c>
       <c r="L83" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930084499521</v>
       </c>
       <c r="M83" t="n">
         <v>13.46644242031963</v>
       </c>
       <c r="N83" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128876776233</v>
       </c>
       <c r="O83" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930368598884</v>
       </c>
       <c r="P83" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0529622687559</v>
       </c>
       <c r="Q83" t="b">
         <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.633402802748919</v>
       </c>
     </row>
     <row r="84">
@@ -5447,25 +5267,25 @@
         <v>82</v>
       </c>
       <c r="L84" t="n">
-        <v>314.1592653589793</v>
+        <v>333.61284776374</v>
       </c>
       <c r="M84" t="n">
         <v>13.46645448345156</v>
       </c>
       <c r="N84" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128876776233</v>
       </c>
       <c r="O84" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930368598884</v>
       </c>
       <c r="P84" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0529622687559</v>
       </c>
       <c r="Q84" t="b">
         <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>-2.633381783460509</v>
       </c>
     </row>
     <row r="85">
@@ -5509,25 +5329,25 @@
         <v>83</v>
       </c>
       <c r="L85" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199900746123</v>
       </c>
       <c r="M85" t="n">
         <v>13.48657873114147</v>
       </c>
       <c r="N85" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128795357786</v>
       </c>
       <c r="O85" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930368598884</v>
       </c>
       <c r="P85" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0529581978335</v>
       </c>
       <c r="Q85" t="b">
         <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.625100897567556</v>
       </c>
     </row>
     <row r="86">
@@ -5571,25 +5391,25 @@
         <v>84</v>
       </c>
       <c r="L86" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935616755819</v>
       </c>
       <c r="M86" t="n">
         <v>13.97553152537241</v>
       </c>
       <c r="N86" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930365246085</v>
       </c>
       <c r="O86" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949720782128</v>
       </c>
       <c r="P86" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940043014107</v>
       </c>
       <c r="Q86" t="b">
         <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>0.000139852832192755</v>
       </c>
     </row>
     <row r="87">
@@ -5633,25 +5453,25 @@
         <v>85</v>
       </c>
       <c r="L87" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935601791496</v>
       </c>
       <c r="M87" t="n">
         <v>13.97745795126847</v>
       </c>
       <c r="N87" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930365246085</v>
       </c>
       <c r="O87" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949720782128</v>
       </c>
       <c r="P87" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940043014107</v>
       </c>
       <c r="Q87" t="b">
         <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>0.0001403256475684955</v>
       </c>
     </row>
     <row r="88">
@@ -5695,25 +5515,25 @@
         <v>86</v>
       </c>
       <c r="L88" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949672377866</v>
       </c>
       <c r="M88" t="n">
         <v>13.98221490934961</v>
       </c>
       <c r="N88" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930365246085</v>
       </c>
       <c r="O88" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949720782128</v>
       </c>
       <c r="P88" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940043014107</v>
       </c>
       <c r="Q88" t="b">
         <v>1</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>-0.0003042510640982599</v>
       </c>
     </row>
     <row r="89">
@@ -5757,25 +5577,25 @@
         <v>87</v>
       </c>
       <c r="L89" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930058181441</v>
       </c>
       <c r="M89" t="n">
         <v>14.46483907120239</v>
       </c>
       <c r="N89" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493007424782</v>
       </c>
       <c r="O89" t="n">
-        <v>314.1592653589793</v>
+        <v>316.52000357171</v>
       </c>
       <c r="P89" t="n">
-        <v>314.1592653589793</v>
+        <v>316.506505498246</v>
       </c>
       <c r="Q89" t="b">
         <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>0.004265214100640513</v>
       </c>
     </row>
     <row r="90">
@@ -5819,25 +5639,25 @@
         <v>88</v>
       </c>
       <c r="L90" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128472937596</v>
       </c>
       <c r="M90" t="n">
         <v>14.46485113433432</v>
       </c>
       <c r="N90" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493007424782</v>
       </c>
       <c r="O90" t="n">
-        <v>314.1592653589793</v>
+        <v>316.52000357171</v>
       </c>
       <c r="P90" t="n">
-        <v>314.1592653589793</v>
+        <v>316.506505498246</v>
       </c>
       <c r="Q90" t="b">
         <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>-5.404736237122409</v>
       </c>
     </row>
     <row r="91">
@@ -5881,25 +5701,25 @@
         <v>89</v>
       </c>
       <c r="L91" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203902427795</v>
       </c>
       <c r="M91" t="n">
         <v>14.4849715926048</v>
       </c>
       <c r="N91" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200099873713</v>
       </c>
       <c r="O91" t="n">
-        <v>314.1592653589793</v>
+        <v>316.52000357171</v>
       </c>
       <c r="P91" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200067795407</v>
       </c>
       <c r="Q91" t="b">
         <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>-0.0001211497632214176</v>
       </c>
     </row>
     <row r="92">
@@ -5943,25 +5763,25 @@
         <v>90</v>
       </c>
       <c r="L92" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930425653542</v>
       </c>
       <c r="M92" t="n">
         <v>14.97392438574944</v>
       </c>
       <c r="N92" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930382973014</v>
       </c>
       <c r="O92" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949730207582</v>
       </c>
       <c r="P92" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940056590298</v>
       </c>
       <c r="Q92" t="b">
         <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>0.0003043007634762063</v>
       </c>
     </row>
     <row r="93">
@@ -6005,25 +5825,25 @@
         <v>91</v>
       </c>
       <c r="L93" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935662898612</v>
       </c>
       <c r="M93" t="n">
         <v>14.97585081164551</v>
       </c>
       <c r="N93" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930382973014</v>
       </c>
       <c r="O93" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949730207582</v>
       </c>
       <c r="P93" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940056590298</v>
       </c>
       <c r="Q93" t="b">
         <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>0.0001388238515476203</v>
       </c>
     </row>
     <row r="94">
@@ -6067,25 +5887,25 @@
         <v>92</v>
       </c>
       <c r="L94" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949672078131</v>
       </c>
       <c r="M94" t="n">
         <v>14.98060776972665</v>
       </c>
       <c r="N94" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930382973014</v>
       </c>
       <c r="O94" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949730207582</v>
       </c>
       <c r="P94" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940056590298</v>
       </c>
       <c r="Q94" t="b">
         <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>-0.0003038126366261551</v>
       </c>
     </row>
     <row r="95">
@@ -6129,25 +5949,25 @@
         <v>93</v>
       </c>
       <c r="L95" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493005652055</v>
       </c>
       <c r="M95" t="n">
         <v>15.4632319315794</v>
       </c>
       <c r="N95" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930021386068</v>
       </c>
       <c r="O95" t="n">
-        <v>314.1592653589793</v>
+        <v>316.52000357171</v>
       </c>
       <c r="P95" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5065028551584</v>
       </c>
       <c r="Q95" t="b">
         <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>0.00426443153034306</v>
       </c>
     </row>
     <row r="96">
@@ -6191,25 +6011,25 @@
         <v>94</v>
       </c>
       <c r="L96" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128473265122</v>
       </c>
       <c r="M96" t="n">
         <v>15.46324399471135</v>
       </c>
       <c r="N96" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930021386068</v>
       </c>
       <c r="O96" t="n">
-        <v>314.1592653589793</v>
+        <v>316.52000357171</v>
       </c>
       <c r="P96" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5065028551584</v>
       </c>
       <c r="Q96" t="b">
         <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>-5.404737127686166</v>
       </c>
     </row>
     <row r="97">
@@ -6253,25 +6073,25 @@
         <v>95</v>
       </c>
       <c r="L97" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200024306247</v>
       </c>
       <c r="M97" t="n">
         <v>15.48336061365892</v>
       </c>
       <c r="N97" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612849690406</v>
       </c>
       <c r="O97" t="n">
-        <v>314.1592653589793</v>
+        <v>316.52000357171</v>
       </c>
       <c r="P97" t="n">
-        <v>314.1592653589793</v>
+        <v>325.066426631058</v>
       </c>
       <c r="Q97" t="b">
         <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.629131617499603</v>
       </c>
     </row>
     <row r="98">
@@ -6315,25 +6135,25 @@
         <v>96</v>
       </c>
       <c r="L98" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930404442985</v>
       </c>
       <c r="M98" t="n">
         <v>15.97231722258589</v>
       </c>
       <c r="N98" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930383625305</v>
       </c>
       <c r="O98" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949711683918</v>
       </c>
       <c r="P98" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940047654612</v>
       </c>
       <c r="Q98" t="b">
         <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>0.0003046886033031271</v>
       </c>
     </row>
     <row r="99">
@@ -6377,25 +6197,25 @@
         <v>97</v>
       </c>
       <c r="L99" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949740776408</v>
       </c>
       <c r="M99" t="n">
         <v>15.97424364848196</v>
       </c>
       <c r="N99" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930383625305</v>
       </c>
       <c r="O99" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949711683918</v>
       </c>
       <c r="P99" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940047654612</v>
       </c>
       <c r="Q99" t="b">
         <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>-0.0003062655737906539</v>
       </c>
     </row>
     <row r="100">
@@ -6439,25 +6259,25 @@
         <v>98</v>
       </c>
       <c r="L100" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949730977892</v>
       </c>
       <c r="M100" t="n">
         <v>15.97900060656309</v>
       </c>
       <c r="N100" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930383625305</v>
       </c>
       <c r="O100" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949711683918</v>
       </c>
       <c r="P100" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940047654612</v>
       </c>
       <c r="Q100" t="b">
         <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>-0.0003059559781304344</v>
       </c>
     </row>
     <row r="101">
@@ -6501,25 +6321,25 @@
         <v>99</v>
       </c>
       <c r="L101" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930132796521</v>
       </c>
       <c r="M101" t="n">
         <v>16.46162476841586</v>
       </c>
       <c r="N101" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930027321008</v>
       </c>
       <c r="O101" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199988886924</v>
       </c>
       <c r="P101" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5065008103966</v>
       </c>
       <c r="Q101" t="b">
         <v>1</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>0.004261375583092253</v>
       </c>
     </row>
     <row r="102">
@@ -6563,25 +6383,25 @@
         <v>100</v>
       </c>
       <c r="L102" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128455768384</v>
       </c>
       <c r="M102" t="n">
         <v>16.46163683154781</v>
       </c>
       <c r="N102" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930027321008</v>
       </c>
       <c r="O102" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199988886924</v>
       </c>
       <c r="P102" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5065008103966</v>
       </c>
       <c r="Q102" t="b">
         <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>-5.404737255835834</v>
       </c>
     </row>
     <row r="103">
@@ -6625,25 +6445,25 @@
         <v>101</v>
       </c>
       <c r="L103" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199976203734</v>
       </c>
       <c r="M103" t="n">
         <v>16.48175726486648</v>
       </c>
       <c r="N103" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128425862997</v>
       </c>
       <c r="O103" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199988886924</v>
       </c>
       <c r="P103" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0664207374961</v>
       </c>
       <c r="Q103" t="b">
         <v>1</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.629131331908396</v>
       </c>
     </row>
     <row r="104">
@@ -6687,25 +6507,25 @@
         <v>102</v>
       </c>
       <c r="L104" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930377771807</v>
       </c>
       <c r="M104" t="n">
         <v>16.97071005909742</v>
       </c>
       <c r="N104" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930372860184</v>
       </c>
       <c r="O104" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949725176785</v>
       </c>
       <c r="P104" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940049018485</v>
       </c>
       <c r="Q104" t="b">
         <v>1</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>0.0003055744035695973</v>
       </c>
     </row>
     <row r="105">
@@ -6749,25 +6569,25 @@
         <v>103</v>
       </c>
       <c r="L105" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935643281086</v>
       </c>
       <c r="M105" t="n">
         <v>16.97263648499348</v>
       </c>
       <c r="N105" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930372860184</v>
       </c>
       <c r="O105" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949725176785</v>
       </c>
       <c r="P105" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940049018485</v>
       </c>
       <c r="Q105" t="b">
         <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>0.0001392044503556455</v>
       </c>
     </row>
     <row r="106">
@@ -6811,25 +6631,25 @@
         <v>104</v>
       </c>
       <c r="L106" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949723935873</v>
       </c>
       <c r="M106" t="n">
         <v>16.97739725774737</v>
       </c>
       <c r="N106" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930372860184</v>
       </c>
       <c r="O106" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949725176785</v>
       </c>
       <c r="P106" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940049018485</v>
       </c>
       <c r="Q106" t="b">
         <v>1</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>-0.0003056903839615543</v>
       </c>
     </row>
     <row r="107">
@@ -6873,25 +6693,25 @@
         <v>105</v>
       </c>
       <c r="L107" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930069255237</v>
       </c>
       <c r="M107" t="n">
         <v>17.46001760490374</v>
       </c>
       <c r="N107" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128491637729</v>
       </c>
       <c r="O107" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199976839511</v>
       </c>
       <c r="P107" t="n">
-        <v>314.1592653589793</v>
+        <v>325.066423423862</v>
       </c>
       <c r="Q107" t="b">
         <v>1</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.637435268778654</v>
       </c>
     </row>
     <row r="108">
@@ -6935,25 +6755,25 @@
         <v>106</v>
       </c>
       <c r="L108" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128499172832</v>
       </c>
       <c r="M108" t="n">
         <v>17.46002966803568</v>
       </c>
       <c r="N108" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128491637729</v>
       </c>
       <c r="O108" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199976839511</v>
       </c>
       <c r="P108" t="n">
-        <v>314.1592653589793</v>
+        <v>325.066423423862</v>
       </c>
       <c r="Q108" t="b">
         <v>1</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>-2.62913234882991</v>
       </c>
     </row>
     <row r="109">
@@ -6997,25 +6817,25 @@
         <v>107</v>
       </c>
       <c r="L109" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199980062439</v>
       </c>
       <c r="M109" t="n">
         <v>17.48015010135435</v>
       </c>
       <c r="N109" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128480980692</v>
       </c>
       <c r="O109" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199976839511</v>
       </c>
       <c r="P109" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0664228910102</v>
       </c>
       <c r="Q109" t="b">
         <v>1</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.629131858270017</v>
       </c>
     </row>
     <row r="110">
@@ -7059,25 +6879,25 @@
         <v>108</v>
       </c>
       <c r="L110" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930401126849</v>
       </c>
       <c r="M110" t="n">
         <v>17.96910289558529</v>
       </c>
       <c r="N110" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935564731936</v>
       </c>
       <c r="O110" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949732469999</v>
       </c>
       <c r="P110" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942648600967</v>
       </c>
       <c r="Q110" t="b">
         <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>0.0003869730190508847</v>
       </c>
     </row>
     <row r="111">
@@ -7121,25 +6941,25 @@
         <v>109</v>
       </c>
       <c r="L111" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493561287317</v>
       </c>
       <c r="M111" t="n">
         <v>17.97102932148136</v>
       </c>
       <c r="N111" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935564731936</v>
       </c>
       <c r="O111" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949732469999</v>
       </c>
       <c r="P111" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942648600967</v>
       </c>
       <c r="Q111" t="b">
         <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>0.0002223019049174546</v>
       </c>
     </row>
     <row r="112">
@@ -7183,25 +7003,25 @@
         <v>110</v>
       </c>
       <c r="L112" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494972739798</v>
       </c>
       <c r="M112" t="n">
         <v>17.97578627956248</v>
       </c>
       <c r="N112" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935564731936</v>
       </c>
       <c r="O112" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949732469999</v>
       </c>
       <c r="P112" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942648600967</v>
       </c>
       <c r="Q112" t="b">
         <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>-0.0002236627262730551</v>
       </c>
     </row>
     <row r="113">
@@ -7245,25 +7065,25 @@
         <v>111</v>
       </c>
       <c r="L113" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930098691743</v>
       </c>
       <c r="M113" t="n">
         <v>18.45840662671885</v>
       </c>
       <c r="N113" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930090131705</v>
       </c>
       <c r="O113" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200030779104</v>
       </c>
       <c r="P113" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5065060455405</v>
       </c>
       <c r="Q113" t="b">
         <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>0.004264107090512503</v>
       </c>
     </row>
     <row r="114">
@@ -7307,25 +7127,25 @@
         <v>112</v>
       </c>
       <c r="L114" t="n">
-        <v>314.1592653589793</v>
+        <v>333.61284375961</v>
       </c>
       <c r="M114" t="n">
         <v>18.45841868985078</v>
       </c>
       <c r="N114" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930090131705</v>
       </c>
       <c r="O114" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200030779104</v>
       </c>
       <c r="P114" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5065060455405</v>
       </c>
       <c r="Q114" t="b">
         <v>1</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>-5.404734938247424</v>
       </c>
     </row>
     <row r="115">
@@ -7369,25 +7189,25 @@
         <v>113</v>
       </c>
       <c r="L115" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930379955985</v>
       </c>
       <c r="M115" t="n">
         <v>18.47854296248777</v>
       </c>
       <c r="N115" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128435143209</v>
       </c>
       <c r="O115" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200030779104</v>
       </c>
       <c r="P115" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0664232961157</v>
       </c>
       <c r="Q115" t="b">
         <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>2.637425672447069</v>
       </c>
     </row>
     <row r="116">
@@ -7431,25 +7251,25 @@
         <v>114</v>
       </c>
       <c r="L116" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935607472273</v>
       </c>
       <c r="M116" t="n">
         <v>18.96749575563242</v>
       </c>
       <c r="N116" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493041840334</v>
       </c>
       <c r="O116" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949678910973</v>
       </c>
       <c r="P116" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940048657156</v>
       </c>
       <c r="Q116" t="b">
         <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>0.0001403244552777849</v>
       </c>
     </row>
     <row r="117">
@@ -7493,25 +7313,25 @@
         <v>115</v>
       </c>
       <c r="L117" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935589194494</v>
       </c>
       <c r="M117" t="n">
         <v>18.96942218152848</v>
       </c>
       <c r="N117" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493041840334</v>
       </c>
       <c r="O117" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949678910973</v>
       </c>
       <c r="P117" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940048657156</v>
       </c>
       <c r="Q117" t="b">
         <v>1</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>0.0001409019631970487</v>
       </c>
     </row>
     <row r="118">
@@ -7555,25 +7375,25 @@
         <v>116</v>
       </c>
       <c r="L118" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949715211828</v>
       </c>
       <c r="M118" t="n">
         <v>18.97417913960961</v>
       </c>
       <c r="N118" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493041840334</v>
       </c>
       <c r="O118" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949678910973</v>
       </c>
       <c r="P118" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940048657156</v>
       </c>
       <c r="Q118" t="b">
         <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>-0.0003054261541457493</v>
       </c>
     </row>
     <row r="119">
@@ -7617,25 +7437,25 @@
         <v>117</v>
       </c>
       <c r="L119" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930138951511</v>
       </c>
       <c r="M119" t="n">
         <v>19.45679948676597</v>
       </c>
       <c r="N119" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930056257696</v>
       </c>
       <c r="O119" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203762938673</v>
       </c>
       <c r="P119" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5066909598185</v>
       </c>
       <c r="Q119" t="b">
         <v>1</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>0.004321256092854053</v>
       </c>
     </row>
     <row r="120">
@@ -7679,25 +7499,25 @@
         <v>118</v>
       </c>
       <c r="L120" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128445192944</v>
       </c>
       <c r="M120" t="n">
         <v>19.45681154989791</v>
       </c>
       <c r="N120" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930056257696</v>
       </c>
       <c r="O120" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203762938673</v>
       </c>
       <c r="P120" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5066909598185</v>
       </c>
       <c r="Q120" t="b">
         <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>-5.404673597136544</v>
       </c>
     </row>
     <row r="121">
@@ -7741,25 +7561,25 @@
         <v>119</v>
       </c>
       <c r="L121" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203741138454</v>
       </c>
       <c r="M121" t="n">
         <v>19.47693582253488</v>
       </c>
       <c r="N121" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128418010185</v>
       </c>
       <c r="O121" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203762938673</v>
       </c>
       <c r="P121" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0666090474429</v>
       </c>
       <c r="Q121" t="b">
         <v>1</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>2.629071918103454</v>
       </c>
     </row>
     <row r="122">
@@ -7803,25 +7623,25 @@
         <v>120</v>
       </c>
       <c r="L122" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493038773986</v>
       </c>
       <c r="M122" t="n">
         <v>19.96588861567953</v>
       </c>
       <c r="N122" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930439535654</v>
       </c>
       <c r="O122" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949758159229</v>
       </c>
       <c r="P122" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940098847442</v>
       </c>
       <c r="Q122" t="b">
         <v>1</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>0.0003068338508382951</v>
       </c>
     </row>
     <row r="123">
@@ -7865,25 +7685,25 @@
         <v>121</v>
       </c>
       <c r="L123" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935613305731</v>
       </c>
       <c r="M123" t="n">
         <v>19.96781504157559</v>
       </c>
       <c r="N123" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930439535654</v>
       </c>
       <c r="O123" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949758159229</v>
       </c>
       <c r="P123" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940098847442</v>
       </c>
       <c r="Q123" t="b">
         <v>1</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>0.0001417259591351971</v>
       </c>
     </row>
     <row r="124">
@@ -7927,25 +7747,25 @@
         <v>122</v>
       </c>
       <c r="L124" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930107030344</v>
       </c>
       <c r="M124" t="n">
         <v>19.97257199965673</v>
       </c>
       <c r="N124" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930439535654</v>
       </c>
       <c r="O124" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949758159229</v>
       </c>
       <c r="P124" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940098847442</v>
       </c>
       <c r="Q124" t="b">
         <v>1</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>0.000315703197717454</v>
       </c>
     </row>
     <row r="125">
@@ -7989,25 +7809,25 @@
         <v>123</v>
       </c>
       <c r="L125" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128470553886</v>
       </c>
       <c r="M125" t="n">
         <v>20.45519234681309</v>
       </c>
       <c r="N125" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128459868684</v>
       </c>
       <c r="O125" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200020058144</v>
       </c>
       <c r="P125" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0664239963414</v>
       </c>
       <c r="Q125" t="b">
         <v>1</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>-2.629131287685182</v>
       </c>
     </row>
     <row r="126">
@@ -8051,25 +7871,25 @@
         <v>124</v>
       </c>
       <c r="L126" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128444058131</v>
       </c>
       <c r="M126" t="n">
         <v>20.45520440994504</v>
       </c>
       <c r="N126" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128459868684</v>
       </c>
       <c r="O126" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200020058144</v>
       </c>
       <c r="P126" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0664239963414</v>
       </c>
       <c r="Q126" t="b">
         <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>-2.629130472597763</v>
       </c>
     </row>
     <row r="127">
@@ -8113,25 +7933,25 @@
         <v>125</v>
       </c>
       <c r="L127" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203775551237</v>
       </c>
       <c r="M127" t="n">
         <v>20.475328682582</v>
       </c>
       <c r="N127" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128506817055</v>
       </c>
       <c r="O127" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200020058144</v>
       </c>
       <c r="P127" t="n">
-        <v>314.1592653589793</v>
+        <v>325.06642634376</v>
       </c>
       <c r="Q127" t="b">
         <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>2.629016132105511</v>
       </c>
     </row>
     <row r="128">
@@ -8175,25 +7995,25 @@
         <v>126</v>
       </c>
       <c r="L128" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935601062048</v>
       </c>
       <c r="M128" t="n">
         <v>20.96428147572665</v>
       </c>
       <c r="N128" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930423463633</v>
       </c>
       <c r="O128" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949668814854</v>
       </c>
       <c r="P128" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940046139243</v>
       </c>
       <c r="Q128" t="b">
         <v>1</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>0.0001404474375577003</v>
       </c>
     </row>
     <row r="129">
@@ -8237,25 +8057,25 @@
         <v>127</v>
       </c>
       <c r="L129" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493559249912</v>
       </c>
       <c r="M129" t="n">
         <v>20.96620790162271</v>
       </c>
       <c r="N129" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930423463633</v>
       </c>
       <c r="O129" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949668814854</v>
       </c>
       <c r="P129" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940046139243</v>
       </c>
       <c r="Q129" t="b">
         <v>1</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>0.0001407179933354819</v>
       </c>
     </row>
     <row r="130">
@@ -8299,25 +8119,25 @@
         <v>128</v>
       </c>
       <c r="L130" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494972694702</v>
       </c>
       <c r="M130" t="n">
         <v>20.97096485970384</v>
       </c>
       <c r="N130" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930423463633</v>
       </c>
       <c r="O130" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949668814854</v>
       </c>
       <c r="P130" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940046139243</v>
       </c>
       <c r="Q130" t="b">
         <v>1</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>-0.0003058764979968487</v>
       </c>
     </row>
     <row r="131">
@@ -8361,25 +8181,25 @@
         <v>129</v>
       </c>
       <c r="L131" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930155241208</v>
       </c>
       <c r="M131" t="n">
         <v>21.45358520686021</v>
       </c>
       <c r="N131" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128470552172</v>
       </c>
       <c r="O131" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930379822863</v>
       </c>
       <c r="P131" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0529425187517</v>
       </c>
       <c r="Q131" t="b">
         <v>1</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>2.633394710505366</v>
       </c>
     </row>
     <row r="132">
@@ -8423,25 +8243,25 @@
         <v>130</v>
       </c>
       <c r="L132" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203728054277</v>
       </c>
       <c r="M132" t="n">
         <v>21.45359726999215</v>
       </c>
       <c r="N132" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128470552172</v>
       </c>
       <c r="O132" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930379822863</v>
       </c>
       <c r="P132" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0529425187517</v>
       </c>
       <c r="Q132" t="b">
         <v>1</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>2.624978456496152</v>
       </c>
     </row>
     <row r="133">
@@ -8485,25 +8305,25 @@
         <v>131</v>
       </c>
       <c r="L133" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930394303518</v>
       </c>
       <c r="M133" t="n">
         <v>21.47372154262911</v>
       </c>
       <c r="N133" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128427491318</v>
       </c>
       <c r="O133" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930379822863</v>
       </c>
       <c r="P133" t="n">
-        <v>314.1592653589793</v>
+        <v>325.052940365709</v>
       </c>
       <c r="Q133" t="b">
         <v>1</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>2.633386711015984</v>
       </c>
     </row>
     <row r="134">
@@ -8547,25 +8367,25 @@
         <v>132</v>
       </c>
       <c r="L134" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935606424712</v>
       </c>
       <c r="M134" t="n">
         <v>21.96267433577376</v>
       </c>
       <c r="N134" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930414946184</v>
       </c>
       <c r="O134" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949693440503</v>
       </c>
       <c r="P134" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940054193343</v>
       </c>
       <c r="Q134" t="b">
         <v>1</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>0.0001405324763004145</v>
       </c>
     </row>
     <row r="135">
@@ -8609,25 +8429,25 @@
         <v>133</v>
       </c>
       <c r="L135" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935556519403</v>
       </c>
       <c r="M135" t="n">
         <v>21.96460076166984</v>
       </c>
       <c r="N135" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930414946184</v>
       </c>
       <c r="O135" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949693440503</v>
       </c>
       <c r="P135" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940054193343</v>
       </c>
       <c r="Q135" t="b">
         <v>1</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>0.0001421092931774837</v>
       </c>
     </row>
     <row r="136">
@@ -8671,25 +8491,25 @@
         <v>134</v>
       </c>
       <c r="L136" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949723969125</v>
       </c>
       <c r="M136" t="n">
         <v>21.96935771975096</v>
       </c>
       <c r="N136" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930414946184</v>
       </c>
       <c r="O136" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949693440503</v>
       </c>
       <c r="P136" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940054193343</v>
       </c>
       <c r="Q136" t="b">
         <v>1</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>-0.0003055279283792345</v>
       </c>
     </row>
     <row r="137">
@@ -8733,25 +8553,25 @@
         <v>135</v>
       </c>
       <c r="L137" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930131088363</v>
       </c>
       <c r="M137" t="n">
         <v>22.45197806690732</v>
       </c>
       <c r="N137" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930069900548</v>
       </c>
       <c r="O137" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200003965199</v>
       </c>
       <c r="P137" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5065036932874</v>
       </c>
       <c r="Q137" t="b">
         <v>1</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>0.004262340360683403</v>
       </c>
     </row>
     <row r="138">
@@ -8795,25 +8615,25 @@
         <v>136</v>
       </c>
       <c r="L138" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612843067546</v>
       </c>
       <c r="M138" t="n">
         <v>22.45199013003927</v>
       </c>
       <c r="N138" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930069900548</v>
       </c>
       <c r="O138" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200003965199</v>
       </c>
       <c r="P138" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5065036932874</v>
       </c>
       <c r="Q138" t="b">
         <v>1</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>-5.404735502950531</v>
       </c>
     </row>
     <row r="139">
@@ -8857,25 +8677,25 @@
         <v>137</v>
       </c>
       <c r="L139" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203929243579</v>
       </c>
       <c r="M139" t="n">
         <v>22.47211058830973</v>
       </c>
       <c r="N139" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128424507029</v>
       </c>
       <c r="O139" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200003965199</v>
       </c>
       <c r="P139" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0664214236114</v>
       </c>
       <c r="Q139" t="b">
         <v>1</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>2.629009930286452</v>
       </c>
     </row>
     <row r="140">
@@ -8919,25 +8739,25 @@
         <v>138</v>
       </c>
       <c r="L140" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930435469172</v>
       </c>
       <c r="M140" t="n">
         <v>22.96106719615042</v>
       </c>
       <c r="N140" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935545092449</v>
       </c>
       <c r="O140" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930136072915</v>
       </c>
       <c r="P140" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4932840582682</v>
       </c>
       <c r="Q140" t="b">
         <v>1</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>7.599256068857585e-05</v>
       </c>
     </row>
     <row r="141">
@@ -8981,25 +8801,25 @@
         <v>139</v>
       </c>
       <c r="L141" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935579793537</v>
       </c>
       <c r="M141" t="n">
         <v>22.96299362204649</v>
       </c>
       <c r="N141" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935545092449</v>
       </c>
       <c r="O141" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930136072915</v>
       </c>
       <c r="P141" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4932840582682</v>
       </c>
       <c r="Q141" t="b">
         <v>1</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>-8.654878294045432e-05</v>
       </c>
     </row>
     <row r="142">
@@ -9043,25 +8863,25 @@
         <v>140</v>
       </c>
       <c r="L142" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949720419701</v>
       </c>
       <c r="M142" t="n">
         <v>22.96775058012763</v>
       </c>
       <c r="N142" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935545092449</v>
       </c>
       <c r="O142" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930136072915</v>
       </c>
       <c r="P142" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4932840582682</v>
       </c>
       <c r="Q142" t="b">
         <v>1</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>-0.0005333395010076458</v>
       </c>
     </row>
     <row r="143">
@@ -9105,25 +8925,25 @@
         <v>141</v>
       </c>
       <c r="L143" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930149451188</v>
       </c>
       <c r="M143" t="n">
         <v>23.45037092728398</v>
       </c>
       <c r="N143" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930084499521</v>
       </c>
       <c r="O143" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203852380529</v>
       </c>
       <c r="P143" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5066968440025</v>
       </c>
       <c r="Q143" t="b">
         <v>1</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>0.004322783378718498</v>
       </c>
     </row>
     <row r="144">
@@ -9167,25 +8987,25 @@
         <v>142</v>
       </c>
       <c r="L144" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128434232093</v>
       </c>
       <c r="M144" t="n">
         <v>23.45038299041592</v>
       </c>
       <c r="N144" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930084499521</v>
       </c>
       <c r="O144" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203852380529</v>
       </c>
       <c r="P144" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5066968440025</v>
       </c>
       <c r="Q144" t="b">
         <v>1</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>-5.404671291248508</v>
       </c>
     </row>
     <row r="145">
@@ -9229,25 +9049,25 @@
         <v>143</v>
       </c>
       <c r="L145" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930368598884</v>
       </c>
       <c r="M145" t="n">
         <v>23.47050344868639</v>
       </c>
       <c r="N145" t="n">
-        <v>314.1592653589793</v>
+        <v>333.61284776374</v>
       </c>
       <c r="O145" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203852380529</v>
       </c>
       <c r="P145" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0666165008964</v>
       </c>
       <c r="Q145" t="b">
         <v>1</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.63748388970122</v>
       </c>
     </row>
     <row r="146">
@@ -9291,25 +9111,25 @@
         <v>144</v>
       </c>
       <c r="L146" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930352462348</v>
       </c>
       <c r="M146" t="n">
         <v>23.95945624183103</v>
       </c>
       <c r="N146" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935616755819</v>
       </c>
       <c r="O146" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949650285195</v>
       </c>
       <c r="P146" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942633520507</v>
       </c>
       <c r="Q146" t="b">
         <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>0.0003880341472584092</v>
       </c>
     </row>
     <row r="147">
@@ -9353,25 +9173,25 @@
         <v>145</v>
       </c>
       <c r="L147" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935624048642</v>
       </c>
       <c r="M147" t="n">
         <v>23.9613826677271</v>
       </c>
       <c r="N147" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935616755819</v>
       </c>
       <c r="O147" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949650285195</v>
       </c>
       <c r="P147" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942633520507</v>
       </c>
       <c r="Q147" t="b">
         <v>1</v>
       </c>
       <c r="R147" t="n">
-        <v>0</v>
+        <v>0.0002214723196281021</v>
       </c>
     </row>
     <row r="148">
@@ -9415,25 +9235,25 @@
         <v>146</v>
       </c>
       <c r="L148" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949720782128</v>
       </c>
       <c r="M148" t="n">
         <v>23.96614344048099</v>
       </c>
       <c r="N148" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935616755819</v>
       </c>
       <c r="O148" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949650285195</v>
       </c>
       <c r="P148" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942633520507</v>
       </c>
       <c r="Q148" t="b">
         <v>1</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>-0.0002239301763573565</v>
       </c>
     </row>
     <row r="149">
@@ -9477,25 +9297,25 @@
         <v>147</v>
       </c>
       <c r="L149" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128411906258</v>
       </c>
       <c r="M149" t="n">
         <v>24.44876378763734</v>
       </c>
       <c r="N149" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930058181441</v>
       </c>
       <c r="O149" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199921168011</v>
       </c>
       <c r="P149" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5064989674726</v>
       </c>
       <c r="Q149" t="b">
         <v>1</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>-5.404736483755834</v>
       </c>
     </row>
     <row r="150">
@@ -9539,25 +9359,25 @@
         <v>148</v>
       </c>
       <c r="L150" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199948966973</v>
       </c>
       <c r="M150" t="n">
         <v>24.44877585076929</v>
       </c>
       <c r="N150" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930058181441</v>
       </c>
       <c r="O150" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199921168011</v>
       </c>
       <c r="P150" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5064989674726</v>
       </c>
       <c r="Q150" t="b">
         <v>1</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>-0.004264029101697098</v>
       </c>
     </row>
     <row r="151">
@@ -9601,25 +9421,25 @@
         <v>149</v>
       </c>
       <c r="L151" t="n">
-        <v>314.1592653589793</v>
+        <v>316.52000357171</v>
       </c>
       <c r="M151" t="n">
         <v>24.46889628408797</v>
       </c>
       <c r="N151" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128472937596</v>
       </c>
       <c r="O151" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199921168011</v>
       </c>
       <c r="P151" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0664197052803</v>
       </c>
       <c r="Q151" t="b">
         <v>1</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>2.629129191910629</v>
       </c>
     </row>
     <row r="152">
@@ -9663,25 +9483,25 @@
         <v>150</v>
       </c>
       <c r="L152" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493554793686</v>
       </c>
       <c r="M152" t="n">
         <v>24.9578490783189</v>
       </c>
       <c r="N152" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930425653542</v>
       </c>
       <c r="O152" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493015470463</v>
       </c>
       <c r="P152" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930290179086</v>
       </c>
       <c r="Q152" t="b">
         <v>1</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>-0.0001661255475626788</v>
       </c>
     </row>
     <row r="153">
@@ -9725,25 +9545,25 @@
         <v>151</v>
       </c>
       <c r="L153" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935631209669</v>
       </c>
       <c r="M153" t="n">
         <v>24.95977550421497</v>
       </c>
       <c r="N153" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930425653542</v>
       </c>
       <c r="O153" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493015470463</v>
       </c>
       <c r="P153" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930290179086</v>
       </c>
       <c r="Q153" t="b">
         <v>1</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>-0.0001687566579144928</v>
       </c>
     </row>
     <row r="154">
@@ -9787,25 +9607,25 @@
         <v>152</v>
       </c>
       <c r="L154" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949730207582</v>
       </c>
       <c r="M154" t="n">
         <v>24.96453627696886</v>
       </c>
       <c r="N154" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930425653542</v>
       </c>
       <c r="O154" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493015470463</v>
       </c>
       <c r="P154" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930290179086</v>
       </c>
       <c r="Q154" t="b">
         <v>1</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>-0.0006142324384228459</v>
       </c>
     </row>
     <row r="155">
@@ -9849,25 +9669,25 @@
         <v>153</v>
       </c>
       <c r="L155" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930139927847</v>
       </c>
       <c r="M155" t="n">
         <v>25.44715662412522</v>
       </c>
       <c r="N155" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493005652055</v>
       </c>
       <c r="O155" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200010784708</v>
       </c>
       <c r="P155" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5065033652629</v>
       </c>
       <c r="Q155" t="b">
         <v>1</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>0.004261957443163489</v>
       </c>
     </row>
     <row r="156">
@@ -9911,25 +9731,25 @@
         <v>154</v>
       </c>
       <c r="L156" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199937486802</v>
       </c>
       <c r="M156" t="n">
         <v>25.44716868725716</v>
       </c>
       <c r="N156" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493005652055</v>
       </c>
       <c r="O156" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200010784708</v>
       </c>
       <c r="P156" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5065033652629</v>
       </c>
       <c r="Q156" t="b">
         <v>1</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>-0.004262276848598923</v>
       </c>
     </row>
     <row r="157">
@@ -9973,25 +9793,25 @@
         <v>155</v>
       </c>
       <c r="L157" t="n">
-        <v>314.1592653589793</v>
+        <v>316.52000357171</v>
       </c>
       <c r="M157" t="n">
         <v>25.46728912057583</v>
       </c>
       <c r="N157" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128473265122</v>
       </c>
       <c r="O157" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200010784708</v>
       </c>
       <c r="P157" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0664242024915</v>
       </c>
       <c r="Q157" t="b">
         <v>1</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>2.629130539011826</v>
       </c>
     </row>
     <row r="158">
@@ -10035,25 +9855,25 @@
         <v>156</v>
       </c>
       <c r="L158" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935538703842</v>
       </c>
       <c r="M158" t="n">
         <v>25.95624191480677</v>
       </c>
       <c r="N158" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930404442985</v>
       </c>
       <c r="O158" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949705238832</v>
       </c>
       <c r="P158" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940054840908</v>
       </c>
       <c r="Q158" t="b">
         <v>1</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>0.00014269265731226</v>
       </c>
     </row>
     <row r="159">
@@ -10097,25 +9917,25 @@
         <v>157</v>
       </c>
       <c r="L159" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935635860169</v>
       </c>
       <c r="M159" t="n">
         <v>25.95816834070283</v>
       </c>
       <c r="N159" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930404442985</v>
       </c>
       <c r="O159" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949705238832</v>
       </c>
       <c r="P159" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940054840908</v>
       </c>
       <c r="Q159" t="b">
         <v>1</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>0.0001396228890060414</v>
       </c>
     </row>
     <row r="160">
@@ -10159,25 +9979,25 @@
         <v>158</v>
       </c>
       <c r="L160" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949711683918</v>
       </c>
       <c r="M160" t="n">
         <v>25.96292911345672</v>
       </c>
       <c r="N160" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930404442985</v>
       </c>
       <c r="O160" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949705238832</v>
       </c>
       <c r="P160" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940054840908</v>
       </c>
       <c r="Q160" t="b">
         <v>1</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>-0.0003051193021796905</v>
       </c>
     </row>
     <row r="161">
@@ -10221,25 +10041,25 @@
         <v>159</v>
       </c>
       <c r="L161" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930134083589</v>
       </c>
       <c r="M161" t="n">
         <v>26.44554946061309</v>
       </c>
       <c r="N161" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930132796521</v>
       </c>
       <c r="O161" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493030620344</v>
       </c>
       <c r="P161" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493021949998</v>
       </c>
       <c r="Q161" t="b">
         <v>1</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>2.69883964065798e-06</v>
       </c>
     </row>
     <row r="162">
@@ -10283,25 +10103,25 @@
         <v>160</v>
       </c>
       <c r="L162" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199951526662</v>
       </c>
       <c r="M162" t="n">
         <v>26.44556152374502</v>
       </c>
       <c r="N162" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930132796521</v>
       </c>
       <c r="O162" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493030620344</v>
       </c>
       <c r="P162" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493021949998</v>
       </c>
       <c r="Q162" t="b">
         <v>1</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>-0.008522526816534537</v>
       </c>
     </row>
     <row r="163">
@@ -10345,25 +10165,25 @@
         <v>161</v>
       </c>
       <c r="L163" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199988886924</v>
       </c>
       <c r="M163" t="n">
         <v>26.46568195706371</v>
       </c>
       <c r="N163" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128455768384</v>
       </c>
       <c r="O163" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493030620344</v>
       </c>
       <c r="P163" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0529380985912</v>
       </c>
       <c r="Q163" t="b">
         <v>1</v>
       </c>
       <c r="R163" t="n">
-        <v>0</v>
+        <v>2.625092164929343</v>
       </c>
     </row>
     <row r="164">
@@ -10407,25 +10227,25 @@
         <v>162</v>
       </c>
       <c r="L164" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930346558558</v>
       </c>
       <c r="M164" t="n">
         <v>26.95463475129464</v>
       </c>
       <c r="N164" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930377771807</v>
       </c>
       <c r="O164" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949640409076</v>
       </c>
       <c r="P164" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940009090442</v>
       </c>
       <c r="Q164" t="b">
         <v>1</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>0.000305299053249275</v>
       </c>
     </row>
     <row r="165">
@@ -10469,25 +10289,25 @@
         <v>163</v>
       </c>
       <c r="L165" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935638957113</v>
       </c>
       <c r="M165" t="n">
         <v>26.95656117719071</v>
       </c>
       <c r="N165" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930377771807</v>
       </c>
       <c r="O165" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949640409076</v>
       </c>
       <c r="P165" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940009090442</v>
       </c>
       <c r="Q165" t="b">
         <v>1</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>0.000138079499656385</v>
       </c>
     </row>
     <row r="166">
@@ -10531,25 +10351,25 @@
         <v>164</v>
       </c>
       <c r="L166" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949725176785</v>
       </c>
       <c r="M166" t="n">
         <v>26.9613219499446</v>
       </c>
       <c r="N166" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930377771807</v>
       </c>
       <c r="O166" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949640409076</v>
       </c>
       <c r="P166" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940009090442</v>
       </c>
       <c r="Q166" t="b">
         <v>1</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>-0.0003069911693742711</v>
       </c>
     </row>
     <row r="167">
@@ -10593,25 +10413,25 @@
         <v>165</v>
       </c>
       <c r="L167" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930162708293</v>
       </c>
       <c r="M167" t="n">
         <v>27.44394229710096</v>
       </c>
       <c r="N167" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930069255237</v>
       </c>
       <c r="O167" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203811689261</v>
       </c>
       <c r="P167" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5066940472249</v>
       </c>
       <c r="Q167" t="b">
         <v>1</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>0.004321480920566056</v>
       </c>
     </row>
     <row r="168">
@@ -10655,25 +10475,25 @@
         <v>166</v>
       </c>
       <c r="L168" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128437266337</v>
       </c>
       <c r="M168" t="n">
         <v>27.4439543602329</v>
       </c>
       <c r="N168" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930069255237</v>
       </c>
       <c r="O168" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203811689261</v>
       </c>
       <c r="P168" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5066940472249</v>
       </c>
       <c r="Q168" t="b">
         <v>1</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>-5.404672318512294</v>
       </c>
     </row>
     <row r="169">
@@ -10717,25 +10537,25 @@
         <v>167</v>
       </c>
       <c r="L169" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199976839511</v>
       </c>
       <c r="M169" t="n">
         <v>27.46407479355159</v>
       </c>
       <c r="N169" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128499172832</v>
       </c>
       <c r="O169" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203811689261</v>
       </c>
       <c r="P169" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0666155431047</v>
       </c>
       <c r="Q169" t="b">
         <v>1</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>2.629189664670506</v>
       </c>
     </row>
     <row r="170">
@@ -10779,25 +10599,25 @@
         <v>168</v>
       </c>
       <c r="L170" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935527530178</v>
       </c>
       <c r="M170" t="n">
         <v>27.95302758778252</v>
       </c>
       <c r="N170" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930401126849</v>
       </c>
       <c r="O170" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930134460378</v>
       </c>
       <c r="P170" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930267793613</v>
       </c>
       <c r="Q170" t="b">
         <v>1</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>-0.0001661880711045782</v>
       </c>
     </row>
     <row r="171">
@@ -10841,25 +10661,25 @@
         <v>169</v>
       </c>
       <c r="L171" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949742216135</v>
       </c>
       <c r="M171" t="n">
         <v>27.95495401367858</v>
       </c>
       <c r="N171" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930401126849</v>
       </c>
       <c r="O171" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930134460378</v>
       </c>
       <c r="P171" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930267793613</v>
       </c>
       <c r="Q171" t="b">
         <v>1</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>-0.0006153191657753965</v>
       </c>
     </row>
     <row r="172">
@@ -10903,25 +10723,25 @@
         <v>170</v>
       </c>
       <c r="L172" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949732469999</v>
       </c>
       <c r="M172" t="n">
         <v>27.95971478643247</v>
       </c>
       <c r="N172" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930401126849</v>
       </c>
       <c r="O172" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930134460378</v>
       </c>
       <c r="P172" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930267793613</v>
       </c>
       <c r="Q172" t="b">
         <v>1</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>-0.0006150112242142569</v>
       </c>
     </row>
     <row r="173">
@@ -10965,25 +10785,25 @@
         <v>171</v>
       </c>
       <c r="L173" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930093159879</v>
       </c>
       <c r="M173" t="n">
         <v>28.44233513358883</v>
       </c>
       <c r="N173" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930098691743</v>
       </c>
       <c r="O173" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203846937026</v>
       </c>
       <c r="P173" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5066972814384</v>
       </c>
       <c r="Q173" t="b">
         <v>1</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>0.004324700098945478</v>
       </c>
     </row>
     <row r="174">
@@ -11027,25 +10847,25 @@
         <v>172</v>
       </c>
       <c r="L174" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128455922499</v>
       </c>
       <c r="M174" t="n">
         <v>28.44234719672078</v>
       </c>
       <c r="N174" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930098691743</v>
       </c>
       <c r="O174" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203846937026</v>
       </c>
       <c r="P174" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5066972814384</v>
       </c>
       <c r="Q174" t="b">
         <v>1</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>-5.404671830877761</v>
       </c>
     </row>
     <row r="175">
@@ -11089,25 +10909,25 @@
         <v>173</v>
       </c>
       <c r="L175" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200030779104</v>
       </c>
       <c r="M175" t="n">
         <v>28.46246763003945</v>
       </c>
       <c r="N175" t="n">
-        <v>314.1592653589793</v>
+        <v>333.61284375961</v>
       </c>
       <c r="O175" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203846937026</v>
       </c>
       <c r="P175" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0666142266563</v>
       </c>
       <c r="Q175" t="b">
         <v>1</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>2.629187611000461</v>
       </c>
     </row>
     <row r="176">
@@ -11151,25 +10971,25 @@
         <v>174</v>
       </c>
       <c r="L176" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930382537314</v>
       </c>
       <c r="M176" t="n">
         <v>28.95142042427038</v>
       </c>
       <c r="N176" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935607472273</v>
       </c>
       <c r="O176" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949662303686</v>
       </c>
       <c r="P176" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494263488798</v>
       </c>
       <c r="Q176" t="b">
         <v>1</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>0.0003871271008537569</v>
       </c>
     </row>
     <row r="177">
@@ -11213,25 +11033,25 @@
         <v>175</v>
       </c>
       <c r="L177" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935642771987</v>
       </c>
       <c r="M177" t="n">
         <v>28.95334685016645</v>
       </c>
       <c r="N177" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935607472273</v>
       </c>
       <c r="O177" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949662303686</v>
       </c>
       <c r="P177" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494263488798</v>
       </c>
       <c r="Q177" t="b">
         <v>1</v>
       </c>
       <c r="R177" t="n">
-        <v>0</v>
+        <v>0.0002209239407746644</v>
       </c>
     </row>
     <row r="178">
@@ -11275,25 +11095,25 @@
         <v>176</v>
       </c>
       <c r="L178" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949678910973</v>
       </c>
       <c r="M178" t="n">
         <v>28.95810380824758</v>
       </c>
       <c r="N178" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935607472273</v>
       </c>
       <c r="O178" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949662303686</v>
       </c>
       <c r="P178" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494263488798</v>
       </c>
       <c r="Q178" t="b">
         <v>1</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>-0.0002225640021391584</v>
       </c>
     </row>
     <row r="179">
@@ -11337,25 +11157,25 @@
         <v>177</v>
       </c>
       <c r="L179" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930073063024</v>
       </c>
       <c r="M179" t="n">
         <v>29.44072415540394</v>
       </c>
       <c r="N179" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930138951511</v>
       </c>
       <c r="O179" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930404458148</v>
       </c>
       <c r="P179" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930271704829</v>
       </c>
       <c r="Q179" t="b">
         <v>1</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>6.276340647204393e-06</v>
       </c>
     </row>
     <row r="180">
@@ -11399,25 +11219,25 @@
         <v>178</v>
       </c>
       <c r="L180" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128510561173</v>
       </c>
       <c r="M180" t="n">
         <v>29.44073621853589</v>
       </c>
       <c r="N180" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930138951511</v>
       </c>
       <c r="O180" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930404458148</v>
       </c>
       <c r="P180" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930271704829</v>
       </c>
       <c r="Q180" t="b">
         <v>1</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>-5.409226243841569</v>
       </c>
     </row>
     <row r="181">
@@ -11461,25 +11281,25 @@
         <v>179</v>
       </c>
       <c r="L181" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203762938673</v>
       </c>
       <c r="M181" t="n">
         <v>29.46086049117286</v>
       </c>
       <c r="N181" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128445192944</v>
       </c>
       <c r="O181" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930404458148</v>
       </c>
       <c r="P181" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0529424825546</v>
       </c>
       <c r="Q181" t="b">
         <v>1</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>2.62497737246149</v>
       </c>
     </row>
     <row r="182">
@@ -11523,25 +11343,25 @@
         <v>180</v>
       </c>
       <c r="L182" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930483601277</v>
       </c>
       <c r="M182" t="n">
         <v>29.94981709901354</v>
       </c>
       <c r="N182" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493038773986</v>
       </c>
       <c r="O182" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949747675478</v>
       </c>
       <c r="P182" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940067707669</v>
       </c>
       <c r="Q182" t="b">
         <v>1</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>0.0003028211020272842</v>
       </c>
     </row>
     <row r="183">
@@ -11585,25 +11405,25 @@
         <v>181</v>
       </c>
       <c r="L183" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935643124924</v>
       </c>
       <c r="M183" t="n">
         <v>29.95174352490961</v>
       </c>
       <c r="N183" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493038773986</v>
       </c>
       <c r="O183" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949747675478</v>
       </c>
       <c r="P183" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940067707669</v>
       </c>
       <c r="Q183" t="b">
         <v>1</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>0.0001397998903751585</v>
       </c>
     </row>
     <row r="184">
@@ -11647,25 +11467,25 @@
         <v>182</v>
       </c>
       <c r="L184" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949758159229</v>
       </c>
       <c r="M184" t="n">
         <v>29.95649666831803</v>
       </c>
       <c r="N184" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493038773986</v>
       </c>
       <c r="O184" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949747675478</v>
       </c>
       <c r="P184" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940067707669</v>
       </c>
       <c r="Q184" t="b">
         <v>1</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>-0.0003061812025695332</v>
       </c>
     </row>
     <row r="185">
@@ -11709,25 +11529,25 @@
         <v>183</v>
       </c>
       <c r="L185" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930096605775</v>
       </c>
       <c r="M185" t="n">
         <v>30.43912083017081</v>
       </c>
       <c r="N185" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128470553886</v>
       </c>
       <c r="O185" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5156936442623</v>
       </c>
       <c r="P185" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0642703498255</v>
       </c>
       <c r="Q185" t="b">
         <v>1</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>2.636789543195206</v>
       </c>
     </row>
     <row r="186">
@@ -11771,25 +11591,25 @@
         <v>184</v>
       </c>
       <c r="L186" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199922130111</v>
       </c>
       <c r="M186" t="n">
         <v>30.43913289330275</v>
       </c>
       <c r="N186" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128470553886</v>
       </c>
       <c r="O186" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5156936442623</v>
       </c>
       <c r="P186" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0642703498255</v>
       </c>
       <c r="Q186" t="b">
         <v>1</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>2.628488860870293</v>
       </c>
     </row>
     <row r="187">
@@ -11833,25 +11653,25 @@
         <v>185</v>
       </c>
       <c r="L187" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200020058144</v>
       </c>
       <c r="M187" t="n">
         <v>30.45925332662144</v>
       </c>
       <c r="N187" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128444058131</v>
       </c>
       <c r="O187" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5156936442623</v>
       </c>
       <c r="P187" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0642690250377</v>
       </c>
       <c r="Q187" t="b">
         <v>1</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>2.628485451461637</v>
       </c>
     </row>
     <row r="188">
@@ -11895,25 +11715,25 @@
         <v>186</v>
       </c>
       <c r="L188" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935571797668</v>
       </c>
       <c r="M188" t="n">
         <v>30.94820612085236</v>
       </c>
       <c r="N188" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935601062048</v>
       </c>
       <c r="O188" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949654888835</v>
       </c>
       <c r="P188" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942627975441</v>
       </c>
       <c r="Q188" t="b">
         <v>1</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>0.0002229480468796119</v>
       </c>
     </row>
     <row r="189">
@@ -11957,25 +11777,25 @@
         <v>187</v>
       </c>
       <c r="L189" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935637803072</v>
       </c>
       <c r="M189" t="n">
         <v>30.95013254674844</v>
       </c>
       <c r="N189" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935601062048</v>
       </c>
       <c r="O189" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949654888835</v>
       </c>
       <c r="P189" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942627975441</v>
       </c>
       <c r="Q189" t="b">
         <v>1</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>0.0002208625302535516</v>
       </c>
     </row>
     <row r="190">
@@ -12019,25 +11839,25 @@
         <v>188</v>
       </c>
       <c r="L190" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949668814854</v>
       </c>
       <c r="M190" t="n">
         <v>30.95488950482956</v>
       </c>
       <c r="N190" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935601062048</v>
       </c>
       <c r="O190" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949654888835</v>
       </c>
       <c r="P190" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942627975441</v>
       </c>
       <c r="Q190" t="b">
         <v>1</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>-0.0002224634137126813</v>
       </c>
     </row>
     <row r="191">
@@ -12081,25 +11901,25 @@
         <v>189</v>
       </c>
       <c r="L191" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930102842295</v>
       </c>
       <c r="M191" t="n">
         <v>31.43751366668234</v>
       </c>
       <c r="N191" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930155241208</v>
       </c>
       <c r="O191" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5153737442754</v>
       </c>
       <c r="P191" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5041946341981</v>
       </c>
       <c r="Q191" t="b">
         <v>1</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>0.003533713030745567</v>
       </c>
     </row>
     <row r="192">
@@ -12143,25 +11963,25 @@
         <v>190</v>
       </c>
       <c r="L192" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128432614034</v>
       </c>
       <c r="M192" t="n">
         <v>31.43752572981429</v>
       </c>
       <c r="N192" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930155241208</v>
       </c>
       <c r="O192" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5153737442754</v>
       </c>
       <c r="P192" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5041946341981</v>
       </c>
       <c r="Q192" t="b">
         <v>1</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>-5.405504545359552</v>
       </c>
     </row>
     <row r="193">
@@ -12205,25 +12025,25 @@
         <v>191</v>
       </c>
       <c r="L193" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930379822863</v>
       </c>
       <c r="M193" t="n">
         <v>31.45764616313296</v>
       </c>
       <c r="N193" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203728054277</v>
       </c>
       <c r="O193" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5153737442754</v>
       </c>
       <c r="P193" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5178732748515</v>
       </c>
       <c r="Q193" t="b">
         <v>1</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>0.00784641079136783</v>
       </c>
     </row>
     <row r="194">
@@ -12267,25 +12087,25 @@
         <v>192</v>
       </c>
       <c r="L194" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930396575569</v>
       </c>
       <c r="M194" t="n">
         <v>31.94659895736389</v>
       </c>
       <c r="N194" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935606424712</v>
       </c>
       <c r="O194" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949651359452</v>
       </c>
       <c r="P194" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942628892082</v>
       </c>
       <c r="Q194" t="b">
         <v>1</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>0.0003864940994913191</v>
       </c>
     </row>
     <row r="195">
@@ -12329,25 +12149,25 @@
         <v>193</v>
       </c>
       <c r="L195" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935645498888</v>
       </c>
       <c r="M195" t="n">
         <v>31.94852538325996</v>
       </c>
       <c r="N195" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935606424712</v>
       </c>
       <c r="O195" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949651359452</v>
       </c>
       <c r="P195" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942628892082</v>
       </c>
       <c r="Q195" t="b">
         <v>1</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>0.000220648334359197</v>
       </c>
     </row>
     <row r="196">
@@ -12391,25 +12211,25 @@
         <v>194</v>
       </c>
       <c r="L196" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949693440503</v>
       </c>
       <c r="M196" t="n">
         <v>31.95328615601385</v>
       </c>
       <c r="N196" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935606424712</v>
       </c>
       <c r="O196" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949651359452</v>
       </c>
       <c r="P196" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942628892082</v>
       </c>
       <c r="Q196" t="b">
         <v>1</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>-0.0002232125270174024</v>
       </c>
     </row>
     <row r="197">
@@ -12453,25 +12273,25 @@
         <v>195</v>
       </c>
       <c r="L197" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930067068296</v>
       </c>
       <c r="M197" t="n">
         <v>32.4359065031702</v>
       </c>
       <c r="N197" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930131088363</v>
       </c>
       <c r="O197" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5266857109433</v>
       </c>
       <c r="P197" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5098494098898</v>
       </c>
       <c r="Q197" t="b">
         <v>1</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>0.005321383549872216</v>
       </c>
     </row>
     <row r="198">
@@ -12515,25 +12335,25 @@
         <v>196</v>
       </c>
       <c r="L198" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128419659346</v>
       </c>
       <c r="M198" t="n">
         <v>32.43591856630215</v>
       </c>
       <c r="N198" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930131088363</v>
       </c>
       <c r="O198" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5266857109433</v>
       </c>
       <c r="P198" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5098494098898</v>
       </c>
       <c r="Q198" t="b">
         <v>1</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>-5.403620957746536</v>
       </c>
     </row>
     <row r="199">
@@ -12577,25 +12397,25 @@
         <v>197</v>
       </c>
       <c r="L199" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200003965199</v>
       </c>
       <c r="M199" t="n">
         <v>32.45603899962083</v>
       </c>
       <c r="N199" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612843067546</v>
       </c>
       <c r="O199" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5266857109433</v>
       </c>
       <c r="P199" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0697643892446</v>
       </c>
       <c r="Q199" t="b">
         <v>1</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>2.630132029900822</v>
       </c>
     </row>
     <row r="200">
@@ -12639,25 +12459,25 @@
         <v>198</v>
       </c>
       <c r="L200" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930389283926</v>
       </c>
       <c r="M200" t="n">
         <v>32.94499179385177</v>
       </c>
       <c r="N200" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930435469172</v>
       </c>
       <c r="O200" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949675569472</v>
       </c>
       <c r="P200" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940055519322</v>
       </c>
       <c r="Q200" t="b">
         <v>1</v>
       </c>
       <c r="R200" t="n">
-        <v>0</v>
+        <v>0.0003054160656046356</v>
       </c>
     </row>
     <row r="201">
@@ -12701,25 +12521,25 @@
         <v>199</v>
       </c>
       <c r="L201" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935597695209</v>
       </c>
       <c r="M201" t="n">
         <v>32.94691821974784</v>
       </c>
       <c r="N201" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930435469172</v>
       </c>
       <c r="O201" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949675569472</v>
       </c>
       <c r="P201" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940055519322</v>
       </c>
       <c r="Q201" t="b">
         <v>1</v>
       </c>
       <c r="R201" t="n">
-        <v>0</v>
+        <v>0.0001408501910105109</v>
       </c>
     </row>
     <row r="202">
@@ -12763,25 +12583,25 @@
         <v>200</v>
       </c>
       <c r="L202" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930136072915</v>
       </c>
       <c r="M202" t="n">
         <v>32.95167517782897</v>
       </c>
       <c r="N202" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930435469172</v>
       </c>
       <c r="O202" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949675569472</v>
       </c>
       <c r="P202" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4940055519322</v>
       </c>
       <c r="Q202" t="b">
         <v>1</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>0.0003134165650231502</v>
       </c>
     </row>
     <row r="203">
@@ -12825,25 +12645,25 @@
         <v>201</v>
       </c>
       <c r="L203" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612836414746</v>
       </c>
       <c r="M203" t="n">
         <v>33.43429933968174</v>
       </c>
       <c r="N203" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930149451188</v>
       </c>
       <c r="O203" t="n">
-        <v>314.1592653589793</v>
+        <v>316.515365025322</v>
       </c>
       <c r="P203" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5041899852204</v>
       </c>
       <c r="Q203" t="b">
         <v>1</v>
       </c>
       <c r="R203" t="n">
-        <v>0</v>
+        <v>-5.40550393039807</v>
       </c>
     </row>
     <row r="204">
@@ -12887,25 +12707,25 @@
         <v>202</v>
       </c>
       <c r="L204" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128479994617</v>
       </c>
       <c r="M204" t="n">
         <v>33.43431140281368</v>
       </c>
       <c r="N204" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930149451188</v>
       </c>
       <c r="O204" t="n">
-        <v>314.1592653589793</v>
+        <v>316.515365025322</v>
       </c>
       <c r="P204" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5041899852204</v>
       </c>
       <c r="Q204" t="b">
         <v>1</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>-5.405507590607339</v>
       </c>
     </row>
     <row r="205">
@@ -12949,25 +12769,25 @@
         <v>203</v>
       </c>
       <c r="L205" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203852380529</v>
       </c>
       <c r="M205" t="n">
         <v>33.45443186108415</v>
       </c>
       <c r="N205" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128434232093</v>
       </c>
       <c r="O205" t="n">
-        <v>314.1592653589793</v>
+        <v>316.515365025322</v>
       </c>
       <c r="P205" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0641042242656</v>
       </c>
       <c r="Q205" t="b">
         <v>1</v>
       </c>
       <c r="R205" t="n">
-        <v>0</v>
+        <v>2.628318191761447</v>
       </c>
     </row>
     <row r="206">
@@ -13011,25 +12831,25 @@
         <v>204</v>
       </c>
       <c r="L206" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493038226619</v>
       </c>
       <c r="M206" t="n">
         <v>33.94338465422879</v>
       </c>
       <c r="N206" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930352462348</v>
       </c>
       <c r="O206" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949735091312</v>
       </c>
       <c r="P206" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494004377683</v>
       </c>
       <c r="Q206" t="b">
         <v>1</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>0.0003052667824965383</v>
       </c>
     </row>
     <row r="207">
@@ -13073,25 +12893,25 @@
         <v>205</v>
       </c>
       <c r="L207" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935677602443</v>
       </c>
       <c r="M207" t="n">
         <v>33.94531108012486</v>
       </c>
       <c r="N207" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930352462348</v>
       </c>
       <c r="O207" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949735091312</v>
       </c>
       <c r="P207" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494004377683</v>
       </c>
       <c r="Q207" t="b">
         <v>1</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>0.0001379544107060759</v>
       </c>
     </row>
     <row r="208">
@@ -13135,25 +12955,25 @@
         <v>206</v>
       </c>
       <c r="L208" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949650285195</v>
       </c>
       <c r="M208" t="n">
         <v>33.950068038206</v>
       </c>
       <c r="N208" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930352462348</v>
       </c>
       <c r="O208" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949735091312</v>
       </c>
       <c r="P208" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494004377683</v>
       </c>
       <c r="Q208" t="b">
         <v>1</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>-0.0003035289209973868</v>
       </c>
     </row>
     <row r="209">
@@ -13197,25 +13017,25 @@
         <v>207</v>
       </c>
       <c r="L209" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930070820501</v>
       </c>
       <c r="M209" t="n">
         <v>34.43268838536236</v>
       </c>
       <c r="N209" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128411906258</v>
       </c>
       <c r="O209" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5157071668045</v>
       </c>
       <c r="P209" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0642741787152</v>
       </c>
       <c r="Q209" t="b">
         <v>1</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>2.636791483259926</v>
       </c>
     </row>
     <row r="210">
@@ -13259,25 +13079,25 @@
         <v>208</v>
       </c>
       <c r="L210" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199845927224</v>
       </c>
       <c r="M210" t="n">
         <v>34.4327004484943</v>
       </c>
       <c r="N210" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128411906258</v>
       </c>
       <c r="O210" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5157071668045</v>
       </c>
       <c r="P210" t="n">
-        <v>314.1592653589793</v>
+        <v>325.0642741787152</v>
       </c>
       <c r="Q210" t="b">
         <v>1</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>2.628492352037182</v>
       </c>
     </row>
     <row r="211">
@@ -13321,25 +13141,25 @@
         <v>209</v>
       </c>
       <c r="L211" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199921168011</v>
       </c>
       <c r="M211" t="n">
         <v>34.45282469618422</v>
       </c>
       <c r="N211" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199948966973</v>
       </c>
       <c r="O211" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5157071668045</v>
       </c>
       <c r="P211" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5178510317509</v>
       </c>
       <c r="Q211" t="b">
         <v>1</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>-0.0006764500148248587</v>
       </c>
     </row>
     <row r="212">
@@ -13383,25 +13203,25 @@
         <v>210</v>
       </c>
       <c r="L212" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930399009428</v>
       </c>
       <c r="M212" t="n">
         <v>34.94177749041516</v>
       </c>
       <c r="N212" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493554793686</v>
       </c>
       <c r="O212" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949949448641</v>
       </c>
       <c r="P212" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494274869275</v>
       </c>
       <c r="Q212" t="b">
         <v>1</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>0.0003902024239721413</v>
       </c>
     </row>
     <row r="213">
@@ -13445,25 +13265,25 @@
         <v>211</v>
       </c>
       <c r="L213" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935629652515</v>
       </c>
       <c r="M213" t="n">
         <v>34.94370391631123</v>
       </c>
       <c r="N213" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493554793686</v>
       </c>
       <c r="O213" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949949448641</v>
       </c>
       <c r="P213" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494274869275</v>
       </c>
       <c r="Q213" t="b">
         <v>1</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>0.0002249342500260099</v>
       </c>
     </row>
     <row r="214">
@@ -13507,25 +13327,25 @@
         <v>212</v>
       </c>
       <c r="L214" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493015470463</v>
       </c>
       <c r="M214" t="n">
         <v>34.94846087439235</v>
       </c>
       <c r="N214" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493554793686</v>
       </c>
       <c r="O214" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949949448641</v>
       </c>
       <c r="P214" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494274869275</v>
       </c>
       <c r="Q214" t="b">
         <v>1</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>0.0003979215145610837</v>
       </c>
     </row>
     <row r="215">
@@ -13569,25 +13389,25 @@
         <v>213</v>
       </c>
       <c r="L215" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930058133309</v>
       </c>
       <c r="M215" t="n">
         <v>35.43108503624514</v>
       </c>
       <c r="N215" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930139927847</v>
       </c>
       <c r="O215" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5154609790848</v>
       </c>
       <c r="P215" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5042374859347</v>
       </c>
       <c r="Q215" t="b">
         <v>1</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>0.003548664211594499</v>
       </c>
     </row>
     <row r="216">
@@ -13631,25 +13451,25 @@
         <v>214</v>
       </c>
       <c r="L216" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128469647055</v>
       </c>
       <c r="M216" t="n">
         <v>35.43109709937708</v>
       </c>
       <c r="N216" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930139927847</v>
       </c>
       <c r="O216" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5154609790848</v>
       </c>
       <c r="P216" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5042374859347</v>
       </c>
       <c r="Q216" t="b">
         <v>1</v>
       </c>
       <c r="R216" t="n">
-        <v>0</v>
+        <v>-5.405491444496402</v>
       </c>
     </row>
     <row r="217">
@@ -13693,25 +13513,25 @@
         <v>215</v>
       </c>
       <c r="L217" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200010784708</v>
       </c>
       <c r="M217" t="n">
         <v>35.45121371832464</v>
       </c>
       <c r="N217" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199937486802</v>
       </c>
       <c r="O217" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5154609790848</v>
       </c>
       <c r="P217" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5177273638825</v>
       </c>
       <c r="Q217" t="b">
         <v>1</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>-0.0007183529994403415</v>
       </c>
     </row>
     <row r="218">
@@ -13755,26 +13575,20 @@
         <v>216</v>
       </c>
       <c r="L218" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930419411776</v>
       </c>
       <c r="M218" t="n">
         <v>35.94017032725162</v>
       </c>
       <c r="N218" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O218" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P218" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4935538703842</v>
+      </c>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
       <c r="Q218" t="b">
-        <v>1</v>
-      </c>
-      <c r="R218" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -13817,26 +13631,20 @@
         <v>217</v>
       </c>
       <c r="L219" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494964929225</v>
       </c>
       <c r="M219" t="n">
         <v>35.94209675314768</v>
       </c>
       <c r="N219" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O219" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P219" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4935538703842</v>
+      </c>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
       <c r="Q219" t="b">
-        <v>1</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -13879,26 +13687,20 @@
         <v>218</v>
       </c>
       <c r="L220" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949705238832</v>
       </c>
       <c r="M220" t="n">
         <v>35.94685752590156</v>
       </c>
       <c r="N220" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O220" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P220" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4935538703842</v>
+      </c>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
       <c r="Q220" t="b">
-        <v>1</v>
-      </c>
-      <c r="R220" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -13941,26 +13743,20 @@
         <v>219</v>
       </c>
       <c r="L221" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128453526853</v>
       </c>
       <c r="M221" t="n">
         <v>36.42947787305793</v>
       </c>
       <c r="N221" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O221" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P221" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930134083589</v>
+      </c>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
       <c r="Q221" t="b">
-        <v>1</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -14003,26 +13799,20 @@
         <v>220</v>
       </c>
       <c r="L222" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612837611058</v>
       </c>
       <c r="M222" t="n">
         <v>36.42948993618987</v>
       </c>
       <c r="N222" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O222" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P222" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930134083589</v>
+      </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
       <c r="Q222" t="b">
-        <v>1</v>
-      </c>
-      <c r="R222" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -14065,26 +13855,20 @@
         <v>221</v>
       </c>
       <c r="L223" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493030620344</v>
       </c>
       <c r="M223" t="n">
         <v>36.44961039446034</v>
       </c>
       <c r="N223" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O223" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P223" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5199951526662</v>
+      </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
       <c r="Q223" t="b">
-        <v>1</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -14127,26 +13911,20 @@
         <v>222</v>
       </c>
       <c r="L224" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930420173263</v>
       </c>
       <c r="M224" t="n">
         <v>36.93856318760498</v>
       </c>
       <c r="N224" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O224" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P224" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930346558558</v>
+      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
       <c r="Q224" t="b">
-        <v>1</v>
-      </c>
-      <c r="R224" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -14189,26 +13967,20 @@
         <v>223</v>
       </c>
       <c r="L225" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935558629183</v>
       </c>
       <c r="M225" t="n">
         <v>36.94048961350105</v>
       </c>
       <c r="N225" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O225" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P225" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930346558558</v>
+      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
       <c r="Q225" t="b">
-        <v>1</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -14251,26 +14023,20 @@
         <v>224</v>
       </c>
       <c r="L226" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949640409076</v>
       </c>
       <c r="M226" t="n">
         <v>36.94524657158218</v>
       </c>
       <c r="N226" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O226" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P226" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930346558558</v>
+      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
       <c r="Q226" t="b">
-        <v>1</v>
-      </c>
-      <c r="R226" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -14313,26 +14079,20 @@
         <v>225</v>
       </c>
       <c r="L227" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930048520816</v>
       </c>
       <c r="M227" t="n">
         <v>37.42785928934572</v>
       </c>
       <c r="N227" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O227" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P227" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930162708293</v>
+      </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
       <c r="Q227" t="b">
-        <v>1</v>
-      </c>
-      <c r="R227" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -14375,26 +14135,20 @@
         <v>226</v>
       </c>
       <c r="L228" t="n">
-        <v>314.1592653589793</v>
+        <v>320.8585680840091</v>
       </c>
       <c r="M228" t="n">
         <v>37.42788249324331</v>
       </c>
       <c r="N228" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O228" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P228" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930162708293</v>
+      </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
       <c r="Q228" t="b">
-        <v>1</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -14437,26 +14191,20 @@
         <v>227</v>
       </c>
       <c r="L229" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203811689261</v>
       </c>
       <c r="M229" t="n">
         <v>37.44800295151378</v>
       </c>
       <c r="N229" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O229" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P229" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>333.6128437266337</v>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
       <c r="Q229" t="b">
-        <v>1</v>
-      </c>
-      <c r="R229" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -14499,26 +14247,20 @@
         <v>228</v>
       </c>
       <c r="L230" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930409556525</v>
       </c>
       <c r="M230" t="n">
         <v>37.93695574465843</v>
       </c>
       <c r="N230" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O230" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P230" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4935527530178</v>
+      </c>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
       <c r="Q230" t="b">
-        <v>1</v>
-      </c>
-      <c r="R230" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -14561,26 +14303,20 @@
         <v>229</v>
       </c>
       <c r="L231" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949721616582</v>
       </c>
       <c r="M231" t="n">
         <v>37.93887835586472</v>
       </c>
       <c r="N231" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O231" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P231" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4935527530178</v>
+      </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
       <c r="Q231" t="b">
-        <v>1</v>
-      </c>
-      <c r="R231" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -14623,26 +14359,20 @@
         <v>230</v>
       </c>
       <c r="L232" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930134460378</v>
       </c>
       <c r="M232" t="n">
         <v>37.94363912861861</v>
       </c>
       <c r="N232" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O232" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P232" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4935527530178</v>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
       <c r="Q232" t="b">
-        <v>1</v>
-      </c>
-      <c r="R232" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -14685,26 +14415,20 @@
         <v>231</v>
       </c>
       <c r="L233" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930117586991</v>
       </c>
       <c r="M233" t="n">
         <v>38.42625184638214</v>
       </c>
       <c r="N233" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O233" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P233" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930093159879</v>
+      </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
       <c r="Q233" t="b">
-        <v>1</v>
-      </c>
-      <c r="R233" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -14747,26 +14471,20 @@
         <v>232</v>
       </c>
       <c r="L234" t="n">
-        <v>314.1592653589793</v>
+        <v>320.8585671402348</v>
       </c>
       <c r="M234" t="n">
         <v>38.42627505027973</v>
       </c>
       <c r="N234" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O234" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P234" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930093159879</v>
+      </c>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
       <c r="Q234" t="b">
-        <v>1</v>
-      </c>
-      <c r="R234" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -14809,26 +14527,20 @@
         <v>233</v>
       </c>
       <c r="L235" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203846937026</v>
       </c>
       <c r="M235" t="n">
         <v>38.4463955085502</v>
       </c>
       <c r="N235" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O235" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P235" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>333.6128455922499</v>
+      </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
       <c r="Q235" t="b">
-        <v>1</v>
-      </c>
-      <c r="R235" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -14871,26 +14583,20 @@
         <v>234</v>
       </c>
       <c r="L236" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935568350299</v>
       </c>
       <c r="M236" t="n">
         <v>38.93534830169485</v>
       </c>
       <c r="N236" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O236" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P236" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930382537314</v>
+      </c>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
       <c r="Q236" t="b">
-        <v>1</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -14933,26 +14639,20 @@
         <v>235</v>
       </c>
       <c r="L237" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935577535929</v>
       </c>
       <c r="M237" t="n">
         <v>38.93727091290115</v>
       </c>
       <c r="N237" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O237" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P237" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930382537314</v>
+      </c>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
       <c r="Q237" t="b">
-        <v>1</v>
-      </c>
-      <c r="R237" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -14995,26 +14695,20 @@
         <v>236</v>
       </c>
       <c r="L238" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949662303686</v>
       </c>
       <c r="M238" t="n">
         <v>38.94203168565503</v>
       </c>
       <c r="N238" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O238" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P238" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930382537314</v>
+      </c>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
       <c r="Q238" t="b">
-        <v>1</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -15057,26 +14751,20 @@
         <v>237</v>
       </c>
       <c r="L239" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493011151319</v>
       </c>
       <c r="M239" t="n">
         <v>39.42267602007139</v>
       </c>
       <c r="N239" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O239" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P239" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930073063024</v>
+      </c>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
       <c r="Q239" t="b">
-        <v>1</v>
-      </c>
-      <c r="R239" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -15119,26 +14807,20 @@
         <v>238</v>
       </c>
       <c r="L240" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5153685157389</v>
       </c>
       <c r="M240" t="n">
         <v>39.42269174847114</v>
       </c>
       <c r="N240" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O240" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P240" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930073063024</v>
+      </c>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
       <c r="Q240" t="b">
-        <v>1</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -15181,26 +14863,20 @@
         <v>239</v>
       </c>
       <c r="L241" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930404458148</v>
       </c>
       <c r="M241" t="n">
         <v>39.44478804116427</v>
       </c>
       <c r="N241" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O241" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P241" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>333.6128510561173</v>
+      </c>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
       <c r="Q241" t="b">
-        <v>1</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -15243,26 +14919,20 @@
         <v>240</v>
       </c>
       <c r="L242" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935543142448</v>
       </c>
       <c r="M242" t="n">
         <v>39.93374083539521</v>
       </c>
       <c r="N242" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O242" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P242" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930483601277</v>
+      </c>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
       <c r="Q242" t="b">
-        <v>1</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -15305,26 +14975,20 @@
         <v>241</v>
       </c>
       <c r="L243" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935526149376</v>
       </c>
       <c r="M243" t="n">
         <v>39.93567107598107</v>
       </c>
       <c r="N243" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O243" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P243" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930483601277</v>
+      </c>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
       <c r="Q243" t="b">
-        <v>1</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -15367,26 +15031,20 @@
         <v>242</v>
       </c>
       <c r="L244" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949747675478</v>
       </c>
       <c r="M244" t="n">
         <v>39.94042421938948</v>
       </c>
       <c r="N244" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O244" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P244" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930483601277</v>
+      </c>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
       <c r="Q244" t="b">
-        <v>1</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -15429,26 +15087,20 @@
         <v>243</v>
       </c>
       <c r="L245" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930121826131</v>
       </c>
       <c r="M245" t="n">
         <v>40.42106855380584</v>
       </c>
       <c r="N245" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O245" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P245" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930096605775</v>
+      </c>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
       <c r="Q245" t="b">
-        <v>1</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -15491,26 +15143,20 @@
         <v>244</v>
       </c>
       <c r="L246" t="n">
-        <v>314.1592653589793</v>
+        <v>326.2334607100112</v>
       </c>
       <c r="M246" t="n">
         <v>40.42108428220559</v>
       </c>
       <c r="N246" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O246" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P246" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.4930096605775</v>
+      </c>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
       <c r="Q246" t="b">
-        <v>1</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -15553,26 +15199,20 @@
         <v>245</v>
       </c>
       <c r="L247" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5156936442623</v>
       </c>
       <c r="M247" t="n">
         <v>40.44318059761931</v>
       </c>
       <c r="N247" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="O247" t="n">
-        <v>314.1592653589793</v>
-      </c>
-      <c r="P247" t="n">
-        <v>314.1592653589793</v>
-      </c>
+        <v>316.5199922130111</v>
+      </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
       <c r="Q247" t="b">
-        <v>1</v>
-      </c>
-      <c r="R247" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -15615,13 +15255,13 @@
         <v>246</v>
       </c>
       <c r="L248" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493045232507</v>
       </c>
       <c r="M248" t="n">
         <v>40.93213339076396</v>
       </c>
       <c r="N248" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935571797668</v>
       </c>
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr"/>
@@ -15671,13 +15311,13 @@
         <v>247</v>
       </c>
       <c r="L249" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949722656391</v>
       </c>
       <c r="M249" t="n">
         <v>40.93405600197026</v>
       </c>
       <c r="N249" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935571797668</v>
       </c>
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr"/>
@@ -15727,13 +15367,13 @@
         <v>248</v>
       </c>
       <c r="L250" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949654888835</v>
       </c>
       <c r="M250" t="n">
         <v>40.93881677472414</v>
       </c>
       <c r="N250" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935571797668</v>
       </c>
       <c r="O250" t="inlineStr"/>
       <c r="P250" t="inlineStr"/>
@@ -15783,13 +15423,13 @@
         <v>249</v>
       </c>
       <c r="L251" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930056206598</v>
       </c>
       <c r="M251" t="n">
         <v>41.41946110914049</v>
       </c>
       <c r="N251" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930102842295</v>
       </c>
       <c r="O251" t="inlineStr"/>
       <c r="P251" t="inlineStr"/>
@@ -15839,13 +15479,13 @@
         <v>250</v>
       </c>
       <c r="L252" t="n">
-        <v>314.1592653589793</v>
+        <v>326.233457029243</v>
       </c>
       <c r="M252" t="n">
         <v>41.41947683754024</v>
       </c>
       <c r="N252" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930102842295</v>
       </c>
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="inlineStr"/>
@@ -15895,13 +15535,13 @@
         <v>251</v>
       </c>
       <c r="L253" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5153737442754</v>
       </c>
       <c r="M253" t="n">
         <v>41.44157313023337</v>
       </c>
       <c r="N253" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128432614034</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr"/>
@@ -15951,13 +15591,13 @@
         <v>252</v>
       </c>
       <c r="L254" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930414080699</v>
       </c>
       <c r="M254" t="n">
         <v>41.93052592446431</v>
       </c>
       <c r="N254" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930396575569</v>
       </c>
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr"/>
@@ -16007,13 +15647,13 @@
         <v>253</v>
       </c>
       <c r="L255" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935539511534</v>
       </c>
       <c r="M255" t="n">
         <v>41.93244853567061</v>
       </c>
       <c r="N255" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930396575569</v>
       </c>
       <c r="O255" t="inlineStr"/>
       <c r="P255" t="inlineStr"/>
@@ -16063,13 +15703,13 @@
         <v>254</v>
       </c>
       <c r="L256" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949651359452</v>
       </c>
       <c r="M256" t="n">
         <v>41.93720930842449</v>
       </c>
       <c r="N256" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930396575569</v>
       </c>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="inlineStr"/>
@@ -16119,13 +15759,13 @@
         <v>255</v>
       </c>
       <c r="L257" t="n">
-        <v>314.1592653589793</v>
+        <v>326.2334643536874</v>
       </c>
       <c r="M257" t="n">
         <v>42.42180567056163</v>
       </c>
       <c r="N257" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930067068296</v>
       </c>
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr"/>
@@ -16175,13 +15815,13 @@
         <v>256</v>
       </c>
       <c r="L258" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5266930890054</v>
       </c>
       <c r="M258" t="n">
         <v>42.42182139896138</v>
       </c>
       <c r="N258" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930067068296</v>
       </c>
       <c r="O258" t="inlineStr"/>
       <c r="P258" t="inlineStr"/>
@@ -16231,13 +15871,13 @@
         <v>257</v>
       </c>
       <c r="L259" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5266857109433</v>
       </c>
       <c r="M259" t="n">
         <v>42.43996603407395</v>
       </c>
       <c r="N259" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128419659346</v>
       </c>
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr"/>
@@ -16287,13 +15927,13 @@
         <v>258</v>
       </c>
       <c r="L260" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930365270935</v>
       </c>
       <c r="M260" t="n">
         <v>42.92891882830489</v>
       </c>
       <c r="N260" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930389283926</v>
       </c>
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr"/>
@@ -16343,13 +15983,13 @@
         <v>259</v>
       </c>
       <c r="L261" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935555479319</v>
       </c>
       <c r="M261" t="n">
         <v>42.93084143951118</v>
       </c>
       <c r="N261" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930389283926</v>
       </c>
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr"/>
@@ -16399,13 +16039,13 @@
         <v>260</v>
       </c>
       <c r="L262" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949675569472</v>
       </c>
       <c r="M262" t="n">
         <v>42.93560221226507</v>
       </c>
       <c r="N262" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930389283926</v>
       </c>
       <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr"/>
@@ -16455,13 +16095,13 @@
         <v>261</v>
       </c>
       <c r="L263" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930070974885</v>
       </c>
       <c r="M263" t="n">
         <v>43.41624654668142</v>
       </c>
       <c r="N263" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612836414746</v>
       </c>
       <c r="O263" t="inlineStr"/>
       <c r="P263" t="inlineStr"/>
@@ -16511,13 +16151,13 @@
         <v>262</v>
       </c>
       <c r="L264" t="n">
-        <v>314.1592653589793</v>
+        <v>353.8522755462858</v>
       </c>
       <c r="M264" t="n">
         <v>43.41625507660382</v>
       </c>
       <c r="N264" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612836414746</v>
       </c>
       <c r="O264" t="inlineStr"/>
       <c r="P264" t="inlineStr"/>
@@ -16567,13 +16207,13 @@
         <v>263</v>
       </c>
       <c r="L265" t="n">
-        <v>314.1592653589793</v>
+        <v>316.515365025322</v>
       </c>
       <c r="M265" t="n">
         <v>43.43835899815091</v>
       </c>
       <c r="N265" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128479994617</v>
       </c>
       <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr"/>
@@ -16623,13 +16263,13 @@
         <v>264</v>
       </c>
       <c r="L266" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930512409626</v>
       </c>
       <c r="M266" t="n">
         <v>43.92731179238185</v>
       </c>
       <c r="N266" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493038226619</v>
       </c>
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr"/>
@@ -16679,13 +16319,13 @@
         <v>265</v>
       </c>
       <c r="L267" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935586474806</v>
       </c>
       <c r="M267" t="n">
         <v>43.92923440358815</v>
       </c>
       <c r="N267" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493038226619</v>
       </c>
       <c r="O267" t="inlineStr"/>
       <c r="P267" t="inlineStr"/>
@@ -16735,13 +16375,13 @@
         <v>266</v>
       </c>
       <c r="L268" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949735091312</v>
       </c>
       <c r="M268" t="n">
         <v>43.93399517634203</v>
       </c>
       <c r="N268" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493038226619</v>
       </c>
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="inlineStr"/>
@@ -16791,13 +16431,13 @@
         <v>267</v>
       </c>
       <c r="L269" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930338221844</v>
       </c>
       <c r="M269" t="n">
         <v>44.41463951075838</v>
       </c>
       <c r="N269" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930070820501</v>
       </c>
       <c r="O269" t="inlineStr"/>
       <c r="P269" t="inlineStr"/>
@@ -16847,13 +16487,13 @@
         <v>268</v>
       </c>
       <c r="L270" t="n">
-        <v>314.1592653589793</v>
+        <v>326.2337572852122</v>
       </c>
       <c r="M270" t="n">
         <v>44.41465523915814</v>
       </c>
       <c r="N270" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930070820501</v>
       </c>
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr"/>
@@ -16903,13 +16543,13 @@
         <v>269</v>
       </c>
       <c r="L271" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5157071668045</v>
       </c>
       <c r="M271" t="n">
         <v>44.43675918341798</v>
       </c>
       <c r="N271" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199845927224</v>
       </c>
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="inlineStr"/>
@@ -16959,13 +16599,13 @@
         <v>270</v>
       </c>
       <c r="L272" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930995056035</v>
       </c>
       <c r="M272" t="n">
         <v>44.92571197656263</v>
       </c>
       <c r="N272" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930399009428</v>
       </c>
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="inlineStr"/>
@@ -17015,13 +16655,13 @@
         <v>271</v>
       </c>
       <c r="L273" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949982632948</v>
       </c>
       <c r="M273" t="n">
         <v>44.92763458776893</v>
       </c>
       <c r="N273" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930399009428</v>
       </c>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr"/>
@@ -17071,13 +16711,13 @@
         <v>272</v>
       </c>
       <c r="L274" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949949448641</v>
       </c>
       <c r="M274" t="n">
         <v>44.93242587790625</v>
       </c>
       <c r="N274" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930399009428</v>
       </c>
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr"/>
@@ -17127,13 +16767,13 @@
         <v>273</v>
       </c>
       <c r="L275" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4931225342144</v>
       </c>
       <c r="M275" t="n">
         <v>45.41307784171541</v>
       </c>
       <c r="N275" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930058133309</v>
       </c>
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr"/>
@@ -17183,13 +16823,13 @@
         <v>274</v>
       </c>
       <c r="L276" t="n">
-        <v>314.1592653589793</v>
+        <v>353.8720428264945</v>
       </c>
       <c r="M276" t="n">
         <v>45.41308637163781</v>
       </c>
       <c r="N276" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930058133309</v>
       </c>
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="inlineStr"/>
@@ -17239,13 +16879,13 @@
         <v>275</v>
       </c>
       <c r="L277" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5154609790848</v>
       </c>
       <c r="M277" t="n">
         <v>45.4351902931849</v>
       </c>
       <c r="N277" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128469647055</v>
       </c>
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr"/>
@@ -17295,13 +16935,13 @@
         <v>276</v>
       </c>
       <c r="L278" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4932882082629</v>
       </c>
       <c r="M278" t="n">
         <v>45.92410494045547</v>
       </c>
       <c r="N278" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930419411776</v>
       </c>
       <c r="O278" t="inlineStr"/>
       <c r="P278" t="inlineStr"/>
@@ -17351,13 +16991,13 @@
         <v>277</v>
       </c>
       <c r="L279" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938104361505</v>
       </c>
       <c r="M279" t="n">
         <v>45.92602755166177</v>
       </c>
       <c r="N279" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930419411776</v>
       </c>
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr"/>
@@ -17407,13 +17047,13 @@
         <v>278</v>
       </c>
       <c r="L280" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4951729044798</v>
       </c>
       <c r="M280" t="n">
         <v>45.93084935918499</v>
       </c>
       <c r="N280" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930419411776</v>
       </c>
       <c r="O280" t="inlineStr"/>
       <c r="P280" t="inlineStr"/>
